--- a/docs/data/jp/xlsx/6946.xlsx
+++ b/docs/data/jp/xlsx/6946.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,6 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -705,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC177"/>
+  <dimension ref="A1:AC200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1156,7 +1159,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>Government Systems Reportable Segments</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1434,7 +1437,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>Industrial Electronic Products Reportable Segments</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -4613,10 +4616,12 @@
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>6350</v>
+      </c>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="29" t="n"/>
       <c r="E50" s="29" t="n"/>
@@ -4651,7 +4656,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B51" s="27" t="n"/>
+      <c r="B51" s="27" t="n">
+        <v>16764810</v>
+      </c>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="29" t="n"/>
       <c r="E51" s="29" t="n"/>
@@ -5850,7 +5857,7 @@
     <row r="77">
       <c r="A77" s="41" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C77" s="39" t="n"/>
@@ -6102,527 +6109,639 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="15">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="15">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="15">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="15">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="15">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="15">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="15">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="15">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="15">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="15">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="15">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="15">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="15">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C82" s="20" t="n">
+      <c r="C83" s="20" t="n">
         <v>3522</v>
       </c>
-      <c r="D82" s="20" t="n">
+      <c r="D83" s="20" t="n">
         <v>3099</v>
       </c>
-      <c r="E82" s="20" t="n">
+      <c r="E83" s="20" t="n">
         <v>3479</v>
       </c>
-      <c r="F82" s="20" t="n">
+      <c r="F83" s="20" t="n">
         <v>2842</v>
       </c>
-      <c r="G82" s="20" t="n">
+      <c r="G83" s="20" t="n">
         <v>3256</v>
       </c>
-      <c r="H82" s="20" t="n">
+      <c r="H83" s="20" t="n">
         <v>3058</v>
       </c>
-      <c r="I82" s="20" t="n">
+      <c r="I83" s="20" t="n">
         <v>4328</v>
       </c>
-      <c r="J82" s="20" t="n">
+      <c r="J83" s="20" t="n">
         <v>3519</v>
       </c>
-      <c r="K82" s="20" t="n">
+      <c r="K83" s="20" t="n">
         <v>5283</v>
       </c>
-      <c r="L82" s="20" t="n">
+      <c r="L83" s="20" t="n">
         <v>4618</v>
       </c>
-      <c r="M82" s="20" t="n">
+      <c r="M83" s="20" t="n">
         <v>6261</v>
       </c>
-      <c r="N82" s="20" t="n">
+      <c r="N83" s="20" t="n">
         <v>5546</v>
       </c>
-      <c r="T82" s="20" t="n">
+      <c r="T83" s="20" t="n">
         <v>3431</v>
       </c>
-      <c r="U82" s="20" t="n">
+      <c r="U83" s="20" t="n">
         <v>3412</v>
       </c>
-      <c r="V82" s="20" t="n">
+      <c r="V83" s="20" t="n">
         <v>3479</v>
       </c>
-      <c r="W82" s="20" t="n">
+      <c r="W83" s="20" t="n">
         <v>4328</v>
       </c>
-      <c r="X82" s="20" t="n">
+      <c r="X83" s="20" t="n">
         <v>6261</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C83" s="12" t="n">
+      <c r="C84" s="12" t="n">
         <v>1541</v>
       </c>
-      <c r="D83" s="12" t="n">
+      <c r="D84" s="12" t="n">
         <v>1485</v>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E84" s="12" t="n">
         <v>1261</v>
       </c>
-      <c r="F83" s="12" t="n">
+      <c r="F84" s="12" t="n">
         <v>1245</v>
       </c>
-      <c r="G83" s="12" t="n">
+      <c r="G84" s="12" t="n">
         <v>1762</v>
       </c>
-      <c r="H83" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>1506</v>
       </c>
-      <c r="I83" s="12" t="n">
+      <c r="I84" s="12" t="n">
         <v>2124</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="J84" s="12" t="n">
         <v>1517</v>
       </c>
-      <c r="K83" s="12" t="n">
+      <c r="K84" s="12" t="n">
         <v>2384</v>
       </c>
-      <c r="L83" s="12" t="n">
+      <c r="L84" s="12" t="n">
         <v>2405</v>
       </c>
-      <c r="M83" s="12" t="n">
+      <c r="M84" s="12" t="n">
         <v>3206</v>
       </c>
-      <c r="N83" s="12" t="n">
+      <c r="N84" s="12" t="n">
         <v>2758</v>
       </c>
-      <c r="T83" s="12" t="n">
+      <c r="T84" s="12" t="n">
         <v>1620</v>
       </c>
-      <c r="U83" s="12" t="n">
+      <c r="U84" s="12" t="n">
         <v>1664</v>
       </c>
-      <c r="V83" s="12" t="n">
+      <c r="V84" s="12" t="n">
         <v>1261</v>
       </c>
-      <c r="W83" s="12" t="n">
+      <c r="W84" s="12" t="n">
         <v>2124</v>
       </c>
-      <c r="X83" s="12" t="n">
+      <c r="X84" s="12" t="n">
         <v>3206</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="n">
-        <v>907</v>
-      </c>
-      <c r="D84" s="20" t="n">
-        <v>886</v>
-      </c>
-      <c r="E84" s="20" t="n">
-        <v>742</v>
-      </c>
-      <c r="F84" s="20" t="n">
-        <v>920</v>
-      </c>
-      <c r="G84" s="20" t="n">
-        <v>938</v>
-      </c>
-      <c r="H84" s="20" t="n">
-        <v>990</v>
-      </c>
-      <c r="I84" s="20" t="n">
-        <v>993</v>
-      </c>
-      <c r="J84" s="20" t="n">
-        <v>935</v>
-      </c>
-      <c r="K84" s="20" t="n">
-        <v>988</v>
-      </c>
-      <c r="L84" s="20" t="n">
-        <v>1012</v>
-      </c>
-      <c r="M84" s="20" t="n">
-        <v>1062</v>
-      </c>
-      <c r="N84" s="20" t="n">
-        <v>1030</v>
-      </c>
-      <c r="T84" s="20" t="n">
-        <v>1092</v>
-      </c>
-      <c r="U84" s="20" t="n">
-        <v>798</v>
-      </c>
-      <c r="V84" s="20" t="n">
-        <v>742</v>
-      </c>
-      <c r="W84" s="20" t="n">
-        <v>993</v>
-      </c>
-      <c r="X84" s="20" t="n">
-        <v>1062</v>
-      </c>
-    </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>599</v>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>518</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>325</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>823</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>517</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>1131</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>582</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>1395</v>
-      </c>
-      <c r="L85" s="12" t="n">
-        <v>1394</v>
-      </c>
-      <c r="M85" s="12" t="n">
-        <v>2144</v>
-      </c>
-      <c r="N85" s="12" t="n">
-        <v>1727</v>
-      </c>
-      <c r="T85" s="12" t="n">
-        <v>528</v>
-      </c>
-      <c r="U85" s="12" t="n">
-        <v>865</v>
-      </c>
-      <c r="V85" s="12" t="n">
-        <v>518</v>
-      </c>
-      <c r="W85" s="12" t="n">
-        <v>1131</v>
-      </c>
-      <c r="X85" s="12" t="n">
-        <v>2144</v>
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G85" s="15">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="15">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="15">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="15">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="15">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="15">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="15">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="15">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="15">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="15">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="15">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="15">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="15">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>수수료 수익</t>
-        </is>
+          <t>판매비와 관리비</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="n">
+        <v>907</v>
+      </c>
+      <c r="D86" s="20" t="n">
+        <v>886</v>
       </c>
       <c r="E86" s="20" t="n">
-        <v>1</v>
+        <v>742</v>
+      </c>
+      <c r="F86" s="20" t="n">
+        <v>920</v>
+      </c>
+      <c r="G86" s="20" t="n">
+        <v>938</v>
+      </c>
+      <c r="H86" s="20" t="n">
+        <v>990</v>
+      </c>
+      <c r="I86" s="20" t="n">
+        <v>993</v>
+      </c>
+      <c r="J86" s="20" t="n">
+        <v>935</v>
+      </c>
+      <c r="K86" s="20" t="n">
+        <v>988</v>
+      </c>
+      <c r="L86" s="20" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M86" s="20" t="n">
+        <v>1062</v>
+      </c>
+      <c r="N86" s="20" t="n">
+        <v>1030</v>
       </c>
       <c r="T86" s="20" t="n">
-        <v>1</v>
+        <v>1092</v>
       </c>
       <c r="U86" s="20" t="n">
-        <v>1</v>
+        <v>798</v>
       </c>
       <c r="V86" s="20" t="n">
-        <v>1</v>
+        <v>742</v>
+      </c>
+      <c r="W86" s="20" t="n">
+        <v>993</v>
+      </c>
+      <c r="X86" s="20" t="n">
+        <v>1062</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>Technical Advisory Fee NOI</t>
-        </is>
-      </c>
-      <c r="C87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M87" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" s="20" t="n">
-        <v>1</v>
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>599</v>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>518</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>325</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>823</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>517</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>1131</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>582</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>1394</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>2144</v>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>1727</v>
+      </c>
+      <c r="T87" s="12" t="n">
+        <v>528</v>
+      </c>
+      <c r="U87" s="12" t="n">
+        <v>865</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>518</v>
+      </c>
+      <c r="W87" s="12" t="n">
+        <v>1131</v>
+      </c>
+      <c r="X87" s="12" t="n">
+        <v>2144</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="18" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C88" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D88" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F88" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H88" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J88" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L88" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T88" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U88" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V88" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="W88" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X88" s="20" t="n">
-        <v>0</v>
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C88" s="15">
+        <f>IF(OR(C87="",C81=""),"",IF(C81&lt;=0,"",IFERROR(C87/C81,"")))</f>
+        <v/>
+      </c>
+      <c r="D88" s="15">
+        <f>IF(OR(D87="",D81=""),"",IF(D81&lt;=0,"",IFERROR(D87/D81,"")))</f>
+        <v/>
+      </c>
+      <c r="E88" s="15">
+        <f>IF(OR(E87="",E81=""),"",IF(E81&lt;=0,"",IFERROR(E87/E81,"")))</f>
+        <v/>
+      </c>
+      <c r="F88" s="15">
+        <f>IF(OR(F87="",F81=""),"",IF(F81&lt;=0,"",IFERROR(F87/F81,"")))</f>
+        <v/>
+      </c>
+      <c r="G88" s="15">
+        <f>IF(OR(G87="",G81=""),"",IF(G81&lt;=0,"",IFERROR(G87/G81,"")))</f>
+        <v/>
+      </c>
+      <c r="H88" s="15">
+        <f>IF(OR(H87="",H81=""),"",IF(H81&lt;=0,"",IFERROR(H87/H81,"")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="15">
+        <f>IF(OR(I87="",I81=""),"",IF(I81&lt;=0,"",IFERROR(I87/I81,"")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="15">
+        <f>IF(OR(J87="",J81=""),"",IF(J81&lt;=0,"",IFERROR(J87/J81,"")))</f>
+        <v/>
+      </c>
+      <c r="K88" s="15">
+        <f>IF(OR(K87="",K81=""),"",IF(K81&lt;=0,"",IFERROR(K87/K81,"")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="15">
+        <f>IF(OR(L87="",L81=""),"",IF(L81&lt;=0,"",IFERROR(L87/L81,"")))</f>
+        <v/>
+      </c>
+      <c r="M88" s="15">
+        <f>IF(OR(M87="",M81=""),"",IF(M81&lt;=0,"",IFERROR(M87/M81,"")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="15">
+        <f>IF(OR(N87="",N81=""),"",IF(N81&lt;=0,"",IFERROR(N87/N81,"")))</f>
+        <v/>
+      </c>
+      <c r="T88" s="15">
+        <f>IF(OR(T87="",T81=""),"",IF(T81&lt;=0,"",IFERROR(T87/T81,"")))</f>
+        <v/>
+      </c>
+      <c r="U88" s="15">
+        <f>IF(OR(U87="",U81=""),"",IF(U81&lt;=0,"",IFERROR(U87/U81,"")))</f>
+        <v/>
+      </c>
+      <c r="V88" s="15">
+        <f>IF(OR(V87="",V81=""),"",IF(V81&lt;=0,"",IFERROR(V87/V81,"")))</f>
+        <v/>
+      </c>
+      <c r="W88" s="15">
+        <f>IF(OR(W87="",W81=""),"",IF(W81&lt;=0,"",IFERROR(W87/W81,"")))</f>
+        <v/>
+      </c>
+      <c r="X88" s="15">
+        <f>IF(OR(X87="",X81=""),"",IF(X81&lt;=0,"",IFERROR(X87/X81,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="inlineStr">
-        <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C89" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G89" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H89" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I89" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="K89" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L89" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="M89" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="N89" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="T89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="U89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V89" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W89" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="X89" s="20" t="n">
-        <v>4</v>
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G89" s="15">
+        <f>IF(OR(G87="",C87=""),"",IF(C87&lt;=0,"",IFERROR(G87/C87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H89" s="15">
+        <f>IF(OR(H87="",D87=""),"",IF(D87&lt;=0,"",IFERROR(H87/D87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I89" s="15">
+        <f>IF(OR(I87="",E87=""),"",IF(E87&lt;=0,"",IFERROR(I87/E87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J89" s="15">
+        <f>IF(OR(J87="",F87=""),"",IF(F87&lt;=0,"",IFERROR(J87/F87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K89" s="15">
+        <f>IF(OR(K87="",G87=""),"",IF(G87&lt;=0,"",IFERROR(K87/G87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L89" s="15">
+        <f>IF(OR(L87="",H87=""),"",IF(H87&lt;=0,"",IFERROR(L87/H87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M89" s="15">
+        <f>IF(OR(M87="",I87=""),"",IF(I87&lt;=0,"",IFERROR(M87/I87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N89" s="15">
+        <f>IF(OR(N87="",J87=""),"",IF(J87&lt;=0,"",IFERROR(N87/J87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T89" s="15">
+        <f>IF(OR(T87="",S87=""),"",IF(S87&lt;=0,"",IFERROR(T87/S87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U89" s="15">
+        <f>IF(OR(U87="",T87=""),"",IF(T87&lt;=0,"",IFERROR(U87/T87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V89" s="15">
+        <f>IF(OR(V87="",U87=""),"",IF(U87&lt;=0,"",IFERROR(V87/U87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W89" s="15">
+        <f>IF(OR(W87="",V87=""),"",IF(V87&lt;=0,"",IFERROR(W87/V87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X89" s="15">
+        <f>IF(OR(X87="",W87=""),"",IF(W87&lt;=0,"",IFERROR(X87/W87-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C90" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="D90" s="20" t="n">
-        <v>8</v>
+          <t>수수료 수익</t>
+        </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="F90" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="G90" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="H90" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="I90" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="J90" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="K90" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="L90" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="M90" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="N90" s="20" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="T90" s="20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U90" s="20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V90" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="W90" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="X90" s="20" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>Technical Advisory Fee NOI</t>
         </is>
       </c>
       <c r="C91" s="20" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="D91" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" s="20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>자기주식 취득비용</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="D92" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="20" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="F92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="H92" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="L92" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="N92" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T92" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U92" s="20" t="n">
+        <v>6</v>
+      </c>
       <c r="V92" s="20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W92" s="20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X92" s="20" t="n">
         <v>0</v>
@@ -6631,185 +6750,134 @@
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C93" s="20" t="n">
         <v>3</v>
       </c>
       <c r="D93" s="20" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E93" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F93" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I93" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="G93" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H93" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="I93" s="20" t="n">
+      <c r="J93" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L93" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M93" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N93" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T93" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="J93" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K93" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="L93" s="20" t="n">
+      <c r="U93" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V93" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="M93" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="N93" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="U93" s="20" t="n">
+      <c r="W93" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X93" s="20" t="n">
         <v>4</v>
-      </c>
-      <c r="V93" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="W93" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="X93" s="20" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D94" s="20" t="n">
         <v>8</v>
       </c>
       <c r="E94" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F94" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G94" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H94" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I94" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="J94" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="K94" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F94" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="G94" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="H94" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="I94" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J94" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K94" s="20" t="n">
-        <v>61</v>
-      </c>
       <c r="L94" s="20" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="M94" s="20" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N94" s="20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T94" s="20" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="U94" s="20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V94" s="20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W94" s="20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="X94" s="20" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>628</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>594</v>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>505</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>308</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>791</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>499</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>1113</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>563</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>1339</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>1361</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>2095</v>
-      </c>
-      <c r="N95" s="12" t="n">
-        <v>1684</v>
-      </c>
-      <c r="T95" s="12" t="n">
-        <v>508</v>
-      </c>
-      <c r="U95" s="12" t="n">
-        <v>855</v>
-      </c>
-      <c r="V95" s="12" t="n">
-        <v>505</v>
-      </c>
-      <c r="W95" s="12" t="n">
-        <v>1113</v>
-      </c>
-      <c r="X95" s="12" t="n">
-        <v>2095</v>
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Land EI</t>
-        </is>
-      </c>
-      <c r="C96" s="20" t="n">
-        <v>0</v>
+          <t>자기주식 취득비용</t>
+        </is>
       </c>
       <c r="D96" s="20" t="n">
         <v>0</v>
@@ -6817,573 +6885,546 @@
       <c r="E96" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="20" t="n">
+      <c r="H96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D97" s="20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E97" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G97" s="20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H97" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I97" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K97" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L97" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="N97" s="20" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U97" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V97" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="W97" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="X97" s="20" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D98" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E98" s="20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F98" s="20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G98" s="20" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L98" s="20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M98" s="20" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N98" s="20" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="T98" s="20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U98" s="20" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="V98" s="20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W98" s="20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X98" s="20" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="18" t="inlineStr">
-        <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="K99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="U99" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="20" t="n">
-        <v>0</v>
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>628</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>594</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>505</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>308</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>791</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>499</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>1113</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>563</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>1339</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>1361</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>2095</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>1684</v>
+      </c>
+      <c r="T99" s="12" t="n">
+        <v>508</v>
+      </c>
+      <c r="U99" s="12" t="n">
+        <v>855</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>505</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>1113</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>2095</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>628</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>594</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>505</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>308</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>791</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>498</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>1113</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>554</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>1339</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>1361</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>2095</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>1684</v>
-      </c>
-      <c r="T100" s="12" t="n">
-        <v>484</v>
-      </c>
-      <c r="U100" s="12" t="n">
-        <v>854</v>
-      </c>
-      <c r="V100" s="12" t="n">
-        <v>505</v>
-      </c>
-      <c r="W100" s="12" t="n">
-        <v>1113</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>2095</v>
+      <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G100" s="15">
+        <f>IF(OR(G99="",C99=""),"",IF(C99&lt;=0,"",IFERROR(G99/C99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H100" s="15">
+        <f>IF(OR(H99="",D99=""),"",IF(D99&lt;=0,"",IFERROR(H99/D99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="15">
+        <f>IF(OR(I99="",E99=""),"",IF(E99&lt;=0,"",IFERROR(I99/E99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="15">
+        <f>IF(OR(J99="",F99=""),"",IF(F99&lt;=0,"",IFERROR(J99/F99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K100" s="15">
+        <f>IF(OR(K99="",G99=""),"",IF(G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L100" s="15">
+        <f>IF(OR(L99="",H99=""),"",IF(H99&lt;=0,"",IFERROR(L99/H99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M100" s="15">
+        <f>IF(OR(M99="",I99=""),"",IF(I99&lt;=0,"",IFERROR(M99/I99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N100" s="15">
+        <f>IF(OR(N99="",J99=""),"",IF(J99&lt;=0,"",IFERROR(N99/J99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T100" s="15">
+        <f>IF(OR(T99="",S99=""),"",IF(S99&lt;=0,"",IFERROR(T99/S99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U100" s="15">
+        <f>IF(OR(U99="",T99=""),"",IF(T99&lt;=0,"",IFERROR(U99/T99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V100" s="15">
+        <f>IF(OR(V99="",U99=""),"",IF(U99&lt;=0,"",IFERROR(V99/U99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W100" s="15">
+        <f>IF(OR(W99="",V99=""),"",IF(V99&lt;=0,"",IFERROR(W99/V99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X100" s="15">
+        <f>IF(OR(X99="",W99=""),"",IF(W99&lt;=0,"",IFERROR(X99/W99-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
+          <t>Gain On Sales Of Land EI</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="U104" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>628</v>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>594</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>505</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>308</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>791</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>498</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>1113</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>554</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>1339</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>1361</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>2095</v>
+      </c>
+      <c r="N105" s="12" t="n">
+        <v>1684</v>
+      </c>
+      <c r="T105" s="12" t="n">
+        <v>484</v>
+      </c>
+      <c r="U105" s="12" t="n">
+        <v>854</v>
+      </c>
+      <c r="V105" s="12" t="n">
+        <v>505</v>
+      </c>
+      <c r="W105" s="12" t="n">
+        <v>1113</v>
+      </c>
+      <c r="X105" s="12" t="n">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
           <t>법인세 등</t>
         </is>
       </c>
-      <c r="C101" s="20" t="n">
+      <c r="C106" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="D101" s="20" t="n">
+      <c r="D106" s="20" t="n">
         <v>173</v>
       </c>
-      <c r="E101" s="20" t="n">
+      <c r="E106" s="20" t="n">
         <v>-251</v>
       </c>
-      <c r="F101" s="20" t="n">
+      <c r="F106" s="20" t="n">
         <v>117</v>
       </c>
-      <c r="G101" s="20" t="n">
+      <c r="G106" s="20" t="n">
         <v>247</v>
       </c>
-      <c r="H101" s="20" t="n">
+      <c r="H106" s="20" t="n">
         <v>167</v>
       </c>
-      <c r="I101" s="20" t="n">
+      <c r="I106" s="20" t="n">
         <v>215</v>
       </c>
-      <c r="J101" s="20" t="n">
+      <c r="J106" s="20" t="n">
         <v>166</v>
       </c>
-      <c r="K101" s="20" t="n">
+      <c r="K106" s="20" t="n">
         <v>427</v>
       </c>
-      <c r="L101" s="20" t="n">
+      <c r="L106" s="20" t="n">
         <v>429</v>
       </c>
-      <c r="M101" s="20" t="n">
+      <c r="M106" s="20" t="n">
         <v>507</v>
       </c>
-      <c r="N101" s="20" t="n">
+      <c r="N106" s="20" t="n">
         <v>535</v>
       </c>
-      <c r="T101" s="20" t="n">
+      <c r="T106" s="20" t="n">
         <v>-15</v>
       </c>
-      <c r="U101" s="20" t="n">
+      <c r="U106" s="20" t="n">
         <v>-60</v>
       </c>
-      <c r="V101" s="20" t="n">
+      <c r="V106" s="20" t="n">
         <v>-251</v>
       </c>
-      <c r="W101" s="20" t="n">
+      <c r="W106" s="20" t="n">
         <v>215</v>
       </c>
-      <c r="X101" s="20" t="n">
+      <c r="X106" s="20" t="n">
         <v>507</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="n">
-        <v>616</v>
-      </c>
-      <c r="D102" s="12" t="n">
-        <v>422</v>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>756</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>191</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>543</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>331</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>899</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>388</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>912</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>931</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>1589</v>
-      </c>
-      <c r="N102" s="12" t="n">
-        <v>1148</v>
-      </c>
-      <c r="T102" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="U102" s="12" t="n">
-        <v>914</v>
-      </c>
-      <c r="V102" s="12" t="n">
-        <v>756</v>
-      </c>
-      <c r="W102" s="12" t="n">
-        <v>899</v>
-      </c>
-      <c r="X102" s="12" t="n">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 순이익</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>616</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>422</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>983</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>191</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>543</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>331</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>899</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>388</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>912</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>931</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>1589</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>1148</v>
-      </c>
-      <c r="T103" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="U103" s="12" t="n">
-        <v>855</v>
-      </c>
-      <c r="V103" s="12" t="n">
-        <v>983</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>899</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="16" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B105" s="42" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="n"/>
-      <c r="G105" s="16" t="n"/>
-      <c r="H105" s="16" t="n"/>
-      <c r="I105" s="16" t="n"/>
-      <c r="J105" s="16" t="n"/>
-      <c r="K105" s="16" t="n"/>
-      <c r="L105" s="16" t="n"/>
-      <c r="M105" s="16" t="n"/>
-      <c r="N105" s="16" t="n"/>
-      <c r="O105" s="16" t="n"/>
-      <c r="P105" s="16" t="n"/>
-      <c r="Q105" s="16" t="n"/>
-      <c r="R105" s="16" t="n"/>
-      <c r="S105" s="16" t="n"/>
-      <c r="T105" s="16" t="n"/>
-      <c r="U105" s="16" t="n"/>
-      <c r="V105" s="16" t="n"/>
-      <c r="W105" s="16" t="n"/>
-      <c r="X105" s="16" t="n"/>
-      <c r="Y105" s="16" t="n"/>
-      <c r="Z105" s="16" t="n"/>
-      <c r="AA105" s="16" t="n"/>
-      <c r="AB105" s="16" t="n"/>
-      <c r="AC105" s="16" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H106" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L106" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M106" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N106" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O106" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P106" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q106" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R106" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S106" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T106" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U106" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V106" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W106" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X106" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y106" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z106" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA106" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB106" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC106" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
       </c>
     </row>
     <row r="107">
@@ -7399,7 +7440,7 @@
         <v>422</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>983</v>
+        <v>756</v>
       </c>
       <c r="F107" s="12" t="n">
         <v>191</v>
@@ -7432,10 +7473,10 @@
         <v>500</v>
       </c>
       <c r="U107" s="12" t="n">
-        <v>855</v>
+        <v>914</v>
       </c>
       <c r="V107" s="12" t="n">
-        <v>983</v>
+        <v>756</v>
       </c>
       <c r="W107" s="12" t="n">
         <v>899</v>
@@ -7445,1111 +7486,1261 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="18" t="inlineStr">
+      <c r="A108" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G108" s="15">
+        <f>IF(OR(G107="",C107=""),"",IF(C107&lt;=0,"",IFERROR(G107/C107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H108" s="15">
+        <f>IF(OR(H107="",D107=""),"",IF(D107&lt;=0,"",IFERROR(H107/D107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I108" s="15">
+        <f>IF(OR(I107="",E107=""),"",IF(E107&lt;=0,"",IFERROR(I107/E107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J108" s="15">
+        <f>IF(OR(J107="",F107=""),"",IF(F107&lt;=0,"",IFERROR(J107/F107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K108" s="15">
+        <f>IF(OR(K107="",G107=""),"",IF(G107&lt;=0,"",IFERROR(K107/G107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L108" s="15">
+        <f>IF(OR(L107="",H107=""),"",IF(H107&lt;=0,"",IFERROR(L107/H107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M108" s="15">
+        <f>IF(OR(M107="",I107=""),"",IF(I107&lt;=0,"",IFERROR(M107/I107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N108" s="15">
+        <f>IF(OR(N107="",J107=""),"",IF(J107&lt;=0,"",IFERROR(N107/J107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T108" s="15">
+        <f>IF(OR(T107="",S107=""),"",IF(S107&lt;=0,"",IFERROR(T107/S107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U108" s="15">
+        <f>IF(OR(U107="",T107=""),"",IF(T107&lt;=0,"",IFERROR(U107/T107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V108" s="15">
+        <f>IF(OR(V107="",U107=""),"",IF(U107&lt;=0,"",IFERROR(V107/U107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W108" s="15">
+        <f>IF(OR(W107="",V107=""),"",IF(V107&lt;=0,"",IFERROR(W107/V107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X108" s="15">
+        <f>IF(OR(X107="",W107=""),"",IF(W107&lt;=0,"",IFERROR(X107/W107-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>616</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>422</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>983</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>543</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>331</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>899</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>388</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>912</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>931</v>
+      </c>
+      <c r="M109" s="12" t="n">
+        <v>1589</v>
+      </c>
+      <c r="N109" s="12" t="n">
+        <v>1148</v>
+      </c>
+      <c r="T109" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="U109" s="12" t="n">
+        <v>855</v>
+      </c>
+      <c r="V109" s="12" t="n">
+        <v>983</v>
+      </c>
+      <c r="W109" s="12" t="n">
+        <v>899</v>
+      </c>
+      <c r="X109" s="12" t="n">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G110" s="15">
+        <f>IF(OR(G109="",C109=""),"",IF(C109&lt;=0,"",IFERROR(G109/C109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H110" s="15">
+        <f>IF(OR(H109="",D109=""),"",IF(D109&lt;=0,"",IFERROR(H109/D109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I110" s="15">
+        <f>IF(OR(I109="",E109=""),"",IF(E109&lt;=0,"",IFERROR(I109/E109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J110" s="15">
+        <f>IF(OR(J109="",F109=""),"",IF(F109&lt;=0,"",IFERROR(J109/F109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K110" s="15">
+        <f>IF(OR(K109="",G109=""),"",IF(G109&lt;=0,"",IFERROR(K109/G109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L110" s="15">
+        <f>IF(OR(L109="",H109=""),"",IF(H109&lt;=0,"",IFERROR(L109/H109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M110" s="15">
+        <f>IF(OR(M109="",I109=""),"",IF(I109&lt;=0,"",IFERROR(M109/I109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N110" s="15">
+        <f>IF(OR(N109="",J109=""),"",IF(J109&lt;=0,"",IFERROR(N109/J109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T110" s="15">
+        <f>IF(OR(T109="",S109=""),"",IF(S109&lt;=0,"",IFERROR(T109/S109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U110" s="15">
+        <f>IF(OR(U109="",T109=""),"",IF(T109&lt;=0,"",IFERROR(U109/T109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V110" s="15">
+        <f>IF(OR(V109="",U109=""),"",IF(U109&lt;=0,"",IFERROR(V109/U109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W110" s="15">
+        <f>IF(OR(W109="",V109=""),"",IF(V109&lt;=0,"",IFERROR(W109/V109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X110" s="15">
+        <f>IF(OR(X109="",W109=""),"",IF(W109&lt;=0,"",IFERROR(X109/W109-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B112" s="42" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="n"/>
+      <c r="D112" s="16" t="n"/>
+      <c r="E112" s="16" t="n"/>
+      <c r="F112" s="16" t="n"/>
+      <c r="G112" s="16" t="n"/>
+      <c r="H112" s="16" t="n"/>
+      <c r="I112" s="16" t="n"/>
+      <c r="J112" s="16" t="n"/>
+      <c r="K112" s="16" t="n"/>
+      <c r="L112" s="16" t="n"/>
+      <c r="M112" s="16" t="n"/>
+      <c r="N112" s="16" t="n"/>
+      <c r="O112" s="16" t="n"/>
+      <c r="P112" s="16" t="n"/>
+      <c r="Q112" s="16" t="n"/>
+      <c r="R112" s="16" t="n"/>
+      <c r="S112" s="16" t="n"/>
+      <c r="T112" s="16" t="n"/>
+      <c r="U112" s="16" t="n"/>
+      <c r="V112" s="16" t="n"/>
+      <c r="W112" s="16" t="n"/>
+      <c r="X112" s="16" t="n"/>
+      <c r="Y112" s="16" t="n"/>
+      <c r="Z112" s="16" t="n"/>
+      <c r="AA112" s="16" t="n"/>
+      <c r="AB112" s="16" t="n"/>
+      <c r="AC112" s="16" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q113" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S113" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T113" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U113" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V113" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W113" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X113" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y113" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z113" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA113" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB113" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC113" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>616</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>422</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>983</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>543</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>331</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>899</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>388</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>912</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>931</v>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>1589</v>
+      </c>
+      <c r="N114" s="12" t="n">
+        <v>1148</v>
+      </c>
+      <c r="T114" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="U114" s="12" t="n">
+        <v>855</v>
+      </c>
+      <c r="V114" s="12" t="n">
+        <v>983</v>
+      </c>
+      <c r="W114" s="12" t="n">
+        <v>899</v>
+      </c>
+      <c r="X114" s="12" t="n">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="20" t="n">
+      <c r="C115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="20" t="n">
         <v>-0</v>
       </c>
-      <c r="E108" s="20" t="n">
+      <c r="E115" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F108" s="20" t="n">
+      <c r="F115" s="20" t="n">
         <v>-0</v>
       </c>
-      <c r="G108" s="20" t="n">
+      <c r="G115" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="20" t="n">
+      <c r="H115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" s="20" t="n">
+      <c r="M115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="W108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="18" t="inlineStr">
+      <c r="W115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
         <is>
           <t>퇴직급여 조정액</t>
         </is>
       </c>
-      <c r="C109" s="20" t="n">
+      <c r="C116" s="20" t="n">
         <v>-25</v>
       </c>
-      <c r="D109" s="20" t="n">
+      <c r="D116" s="20" t="n">
         <v>-25</v>
       </c>
-      <c r="E109" s="20" t="n">
+      <c r="E116" s="20" t="n">
         <v>202</v>
       </c>
-      <c r="F109" s="20" t="n">
+      <c r="F116" s="20" t="n">
         <v>-11</v>
       </c>
-      <c r="G109" s="20" t="n">
+      <c r="G116" s="20" t="n">
         <v>-11</v>
       </c>
-      <c r="H109" s="20" t="n">
+      <c r="H116" s="20" t="n">
         <v>-12</v>
       </c>
-      <c r="I109" s="20" t="n">
+      <c r="I116" s="20" t="n">
         <v>-161</v>
       </c>
-      <c r="J109" s="20" t="n">
+      <c r="J116" s="20" t="n">
         <v>-15</v>
       </c>
-      <c r="K109" s="20" t="n">
+      <c r="K116" s="20" t="n">
         <v>-15</v>
       </c>
-      <c r="L109" s="20" t="n">
+      <c r="L116" s="20" t="n">
         <v>-13</v>
       </c>
-      <c r="M109" s="20" t="n">
+      <c r="M116" s="20" t="n">
         <v>452</v>
       </c>
-      <c r="N109" s="20" t="n">
+      <c r="N116" s="20" t="n">
         <v>-23</v>
       </c>
-      <c r="T109" s="20" t="n">
+      <c r="T116" s="20" t="n">
         <v>-108</v>
       </c>
-      <c r="U109" s="20" t="n">
+      <c r="U116" s="20" t="n">
         <v>-338</v>
       </c>
-      <c r="V109" s="20" t="n">
+      <c r="V116" s="20" t="n">
         <v>202</v>
       </c>
-      <c r="W109" s="20" t="n">
+      <c r="W116" s="20" t="n">
         <v>-161</v>
       </c>
-      <c r="X109" s="20" t="n">
+      <c r="X116" s="20" t="n">
         <v>452</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="18" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C110" s="20" t="n">
-        <v>-25</v>
-      </c>
-      <c r="D110" s="20" t="n">
-        <v>-25</v>
-      </c>
-      <c r="E110" s="20" t="n">
-        <v>203</v>
-      </c>
-      <c r="F110" s="20" t="n">
-        <v>-12</v>
-      </c>
-      <c r="G110" s="20" t="n">
-        <v>-12</v>
-      </c>
-      <c r="H110" s="20" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I110" s="20" t="n">
-        <v>-191</v>
-      </c>
-      <c r="J110" s="20" t="n">
-        <v>-14</v>
-      </c>
-      <c r="K110" s="20" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L110" s="20" t="n">
-        <v>-13</v>
-      </c>
-      <c r="M110" s="20" t="n">
-        <v>453</v>
-      </c>
-      <c r="N110" s="20" t="n">
-        <v>-22</v>
-      </c>
-      <c r="T110" s="20" t="n">
-        <v>-107</v>
-      </c>
-      <c r="U110" s="20" t="n">
-        <v>-337</v>
-      </c>
-      <c r="V110" s="20" t="n">
-        <v>203</v>
-      </c>
-      <c r="W110" s="20" t="n">
-        <v>-191</v>
-      </c>
-      <c r="X110" s="20" t="n">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="n">
-        <v>592</v>
-      </c>
-      <c r="D111" s="12" t="n">
-        <v>396</v>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>178</v>
-      </c>
-      <c r="G111" s="12" t="n">
-        <v>532</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>320</v>
-      </c>
-      <c r="I111" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>373</v>
-      </c>
-      <c r="K111" s="12" t="n">
-        <v>897</v>
-      </c>
-      <c r="L111" s="12" t="n">
-        <v>919</v>
-      </c>
-      <c r="M111" s="12" t="n">
-        <v>2042</v>
-      </c>
-      <c r="N111" s="12" t="n">
-        <v>1125</v>
-      </c>
-      <c r="T111" s="12" t="n">
-        <v>392</v>
-      </c>
-      <c r="U111" s="12" t="n">
-        <v>517</v>
-      </c>
-      <c r="V111" s="12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="W111" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="X111" s="12" t="n">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="n">
-        <v>592</v>
-      </c>
-      <c r="D112" s="12" t="n">
-        <v>396</v>
-      </c>
-      <c r="E112" s="12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="F112" s="12" t="n">
-        <v>178</v>
-      </c>
-      <c r="G112" s="12" t="n">
-        <v>532</v>
-      </c>
-      <c r="H112" s="12" t="n">
-        <v>320</v>
-      </c>
-      <c r="I112" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="J112" s="12" t="n">
-        <v>373</v>
-      </c>
-      <c r="K112" s="12" t="n">
-        <v>897</v>
-      </c>
-      <c r="L112" s="12" t="n">
-        <v>919</v>
-      </c>
-      <c r="M112" s="12" t="n">
-        <v>2042</v>
-      </c>
-      <c r="N112" s="12" t="n">
-        <v>1125</v>
-      </c>
-      <c r="T112" s="12" t="n">
-        <v>392</v>
-      </c>
-      <c r="U112" s="12" t="n">
-        <v>517</v>
-      </c>
-      <c r="V112" s="12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="W112" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="X112" s="12" t="n">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>비지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
-        <is>
-          <t>부문 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B115" s="42" t="inlineStr">
-        <is>
-          <t>부문 · 항목</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="n"/>
-      <c r="D115" s="16" t="n"/>
-      <c r="E115" s="16" t="n"/>
-      <c r="F115" s="16" t="n"/>
-      <c r="G115" s="16" t="n"/>
-      <c r="H115" s="16" t="n"/>
-      <c r="I115" s="16" t="n"/>
-      <c r="J115" s="16" t="n"/>
-      <c r="K115" s="16" t="n"/>
-      <c r="L115" s="16" t="n"/>
-      <c r="M115" s="16" t="n"/>
-      <c r="N115" s="16" t="n"/>
-      <c r="O115" s="16" t="n"/>
-      <c r="P115" s="16" t="n"/>
-      <c r="Q115" s="16" t="n"/>
-      <c r="R115" s="16" t="n"/>
-      <c r="S115" s="16" t="n"/>
-      <c r="T115" s="16" t="n"/>
-      <c r="U115" s="16" t="n"/>
-      <c r="V115" s="16" t="n"/>
-      <c r="W115" s="16" t="n"/>
-      <c r="X115" s="16" t="n"/>
-      <c r="Y115" s="16" t="n"/>
-      <c r="Z115" s="16" t="n"/>
-      <c r="AA115" s="16" t="n"/>
-      <c r="AB115" s="16" t="n"/>
-      <c r="AC115" s="16" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J116" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L116" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M116" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N116" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O116" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P116" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q116" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R116" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S116" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T116" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U116" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V116" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W116" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X116" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y116" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z116" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA116" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB116" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC116" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>기타포괄손익 합계</t>
         </is>
       </c>
       <c r="C117" s="20" t="n">
-        <v>4064</v>
+        <v>-25</v>
       </c>
       <c r="D117" s="20" t="n">
-        <v>3804</v>
+        <v>-25</v>
+      </c>
+      <c r="E117" s="20" t="n">
+        <v>203</v>
       </c>
       <c r="F117" s="20" t="n">
-        <v>3341</v>
+        <v>-12</v>
       </c>
       <c r="G117" s="20" t="n">
-        <v>3729</v>
+        <v>-12</v>
       </c>
       <c r="H117" s="20" t="n">
-        <v>3860</v>
+        <v>-11</v>
       </c>
       <c r="I117" s="20" t="n">
-        <v>5101</v>
+        <v>-191</v>
       </c>
       <c r="J117" s="20" t="n">
-        <v>4019</v>
+        <v>-14</v>
       </c>
       <c r="K117" s="20" t="n">
-        <v>6139</v>
+        <v>-15</v>
       </c>
       <c r="L117" s="20" t="n">
-        <v>5844</v>
+        <v>-13</v>
       </c>
       <c r="M117" s="20" t="n">
-        <v>7856</v>
+        <v>453</v>
       </c>
       <c r="N117" s="20" t="n">
-        <v>7240</v>
+        <v>-22</v>
+      </c>
+      <c r="T117" s="20" t="n">
+        <v>-107</v>
+      </c>
+      <c r="U117" s="20" t="n">
+        <v>-337</v>
+      </c>
+      <c r="V117" s="20" t="n">
+        <v>203</v>
       </c>
       <c r="W117" s="20" t="n">
-        <v>5101</v>
+        <v>-191</v>
       </c>
       <c r="X117" s="20" t="n">
-        <v>7856</v>
+        <v>453</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="18" t="inlineStr">
-        <is>
-          <t>부문 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D118" s="20" t="n">
-        <v>779</v>
-      </c>
-      <c r="F118" s="20" t="n">
-        <v>745</v>
-      </c>
-      <c r="G118" s="20" t="n">
-        <v>1290</v>
-      </c>
-      <c r="H118" s="20" t="n">
-        <v>705</v>
-      </c>
-      <c r="I118" s="20" t="n">
-        <v>1351</v>
-      </c>
-      <c r="J118" s="20" t="n">
-        <v>1017</v>
-      </c>
-      <c r="K118" s="20" t="n">
-        <v>1528</v>
-      </c>
-      <c r="L118" s="20" t="n">
-        <v>1179</v>
-      </c>
-      <c r="M118" s="20" t="n">
-        <v>1611</v>
-      </c>
-      <c r="N118" s="20" t="n">
-        <v>1064</v>
-      </c>
-      <c r="W118" s="20" t="n">
-        <v>1351</v>
-      </c>
-      <c r="X118" s="20" t="n">
-        <v>1611</v>
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="n">
+        <v>592</v>
+      </c>
+      <c r="D118" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>1188</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>532</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>707</v>
+      </c>
+      <c r="J118" s="12" t="n">
+        <v>373</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>897</v>
+      </c>
+      <c r="L118" s="12" t="n">
+        <v>919</v>
+      </c>
+      <c r="M118" s="12" t="n">
+        <v>2042</v>
+      </c>
+      <c r="N118" s="12" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T118" s="12" t="n">
+        <v>392</v>
+      </c>
+      <c r="U118" s="12" t="n">
+        <v>517</v>
+      </c>
+      <c r="V118" s="12" t="n">
+        <v>1188</v>
+      </c>
+      <c r="W118" s="12" t="n">
+        <v>707</v>
+      </c>
+      <c r="X118" s="12" t="n">
+        <v>2042</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="F119" s="20" t="n">
-        <v>4087</v>
-      </c>
-      <c r="G119" s="20" t="n">
-        <v>5019</v>
-      </c>
-      <c r="H119" s="20" t="n">
-        <v>4564</v>
-      </c>
-      <c r="I119" s="20" t="n">
-        <v>6452</v>
-      </c>
-      <c r="J119" s="20" t="n">
-        <v>5037</v>
-      </c>
-      <c r="K119" s="20" t="n">
-        <v>7666</v>
-      </c>
-      <c r="L119" s="20" t="n">
-        <v>7023</v>
-      </c>
-      <c r="M119" s="20" t="n">
-        <v>9468</v>
-      </c>
-      <c r="N119" s="20" t="n">
-        <v>8304</v>
-      </c>
-      <c r="W119" s="20" t="n">
-        <v>6452</v>
-      </c>
-      <c r="X119" s="20" t="n">
-        <v>9468</v>
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>592</v>
+      </c>
+      <c r="D119" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>1188</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>532</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>707</v>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>373</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>897</v>
+      </c>
+      <c r="L119" s="12" t="n">
+        <v>919</v>
+      </c>
+      <c r="M119" s="12" t="n">
+        <v>2042</v>
+      </c>
+      <c r="N119" s="12" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T119" s="12" t="n">
+        <v>392</v>
+      </c>
+      <c r="U119" s="12" t="n">
+        <v>517</v>
+      </c>
+      <c r="V119" s="12" t="n">
+        <v>1188</v>
+      </c>
+      <c r="W119" s="12" t="n">
+        <v>707</v>
+      </c>
+      <c r="X119" s="12" t="n">
+        <v>2042</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="F120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="n">
-        <v>5064</v>
-      </c>
-      <c r="D121" s="12" t="n">
-        <v>4584</v>
-      </c>
-      <c r="F121" s="12" t="n">
-        <v>4087</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>5019</v>
-      </c>
-      <c r="H121" s="12" t="n">
-        <v>4564</v>
-      </c>
-      <c r="I121" s="12" t="n">
-        <v>6452</v>
-      </c>
-      <c r="J121" s="12" t="n">
-        <v>5037</v>
-      </c>
-      <c r="K121" s="12" t="n">
-        <v>7666</v>
-      </c>
-      <c r="L121" s="12" t="n">
-        <v>7023</v>
-      </c>
-      <c r="M121" s="12" t="n">
-        <v>9468</v>
-      </c>
-      <c r="N121" s="12" t="n">
-        <v>8304</v>
-      </c>
-      <c r="W121" s="12" t="n">
-        <v>6452</v>
-      </c>
-      <c r="X121" s="12" t="n">
-        <v>9468</v>
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>비지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="18" t="inlineStr">
-        <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="C122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="A122" s="16" t="inlineStr">
+        <is>
+          <t>부문 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B122" s="42" t="inlineStr">
+        <is>
+          <t>부문 · 항목</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="n"/>
+      <c r="D122" s="16" t="n"/>
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="16" t="n"/>
+      <c r="G122" s="16" t="n"/>
+      <c r="H122" s="16" t="n"/>
+      <c r="I122" s="16" t="n"/>
+      <c r="J122" s="16" t="n"/>
+      <c r="K122" s="16" t="n"/>
+      <c r="L122" s="16" t="n"/>
+      <c r="M122" s="16" t="n"/>
+      <c r="N122" s="16" t="n"/>
+      <c r="O122" s="16" t="n"/>
+      <c r="P122" s="16" t="n"/>
+      <c r="Q122" s="16" t="n"/>
+      <c r="R122" s="16" t="n"/>
+      <c r="S122" s="16" t="n"/>
+      <c r="T122" s="16" t="n"/>
+      <c r="U122" s="16" t="n"/>
+      <c r="V122" s="16" t="n"/>
+      <c r="W122" s="16" t="n"/>
+      <c r="X122" s="16" t="n"/>
+      <c r="Y122" s="16" t="n"/>
+      <c r="Z122" s="16" t="n"/>
+      <c r="AA122" s="16" t="n"/>
+      <c r="AB122" s="16" t="n"/>
+      <c r="AC122" s="16" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="18" t="inlineStr">
-        <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="C123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="K123" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="L123" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="M123" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="N123" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="W123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" s="20" t="n">
-        <v>47</v>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q123" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S123" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T123" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U123" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V123" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W123" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X123" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y123" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z123" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA123" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB123" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC123" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
-        </is>
+          <t>부문 · 외부 고객 매출</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="n">
+        <v>4064</v>
+      </c>
+      <c r="D124" s="20" t="n">
+        <v>3804</v>
       </c>
       <c r="F124" s="20" t="n">
-        <v>0</v>
+        <v>3341</v>
       </c>
       <c r="G124" s="20" t="n">
-        <v>0</v>
+        <v>3729</v>
       </c>
       <c r="H124" s="20" t="n">
-        <v>0</v>
+        <v>3860</v>
       </c>
       <c r="I124" s="20" t="n">
-        <v>0</v>
+        <v>5101</v>
       </c>
       <c r="J124" s="20" t="n">
-        <v>29</v>
+        <v>4019</v>
       </c>
       <c r="K124" s="20" t="n">
-        <v>51</v>
+        <v>6139</v>
       </c>
       <c r="L124" s="20" t="n">
-        <v>46</v>
+        <v>5844</v>
       </c>
       <c r="M124" s="20" t="n">
-        <v>47</v>
+        <v>7856</v>
       </c>
       <c r="N124" s="20" t="n">
-        <v>21</v>
+        <v>7240</v>
       </c>
       <c r="W124" s="20" t="n">
-        <v>0</v>
+        <v>5101</v>
       </c>
       <c r="X124" s="20" t="n">
-        <v>47</v>
+        <v>7856</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="F125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="20" t="n">
-        <v>-29</v>
-      </c>
-      <c r="K125" s="20" t="n">
-        <v>-51</v>
-      </c>
-      <c r="L125" s="20" t="n">
-        <v>-46</v>
-      </c>
-      <c r="M125" s="20" t="n">
-        <v>-47</v>
-      </c>
-      <c r="N125" s="20" t="n">
-        <v>-21</v>
-      </c>
-      <c r="W125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" s="20" t="n">
-        <v>-47</v>
+      <c r="A125" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G125" s="15">
+        <f>IF(OR(G124="",C124=""),"",IF(C124&lt;=0,"",IFERROR(G124/C124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H125" s="15">
+        <f>IF(OR(H124="",D124=""),"",IF(D124&lt;=0,"",IFERROR(H124/D124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I125" s="15">
+        <f>IF(OR(I124="",E124=""),"",IF(E124&lt;=0,"",IFERROR(I124/E124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J125" s="15">
+        <f>IF(OR(J124="",F124=""),"",IF(F124&lt;=0,"",IFERROR(J124/F124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K125" s="15">
+        <f>IF(OR(K124="",G124=""),"",IF(G124&lt;=0,"",IFERROR(K124/G124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L125" s="15">
+        <f>IF(OR(L124="",H124=""),"",IF(H124&lt;=0,"",IFERROR(L124/H124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M125" s="15">
+        <f>IF(OR(M124="",I124=""),"",IF(I124&lt;=0,"",IFERROR(M124/I124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N125" s="15">
+        <f>IF(OR(N124="",J124=""),"",IF(J124&lt;=0,"",IFERROR(N124/J124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W125" s="15">
+        <f>IF(OR(W124="",V124=""),"",IF(V124&lt;=0,"",IFERROR(W124/V124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X125" s="15">
+        <f>IF(OR(X124="",W124=""),"",IF(W124&lt;=0,"",IFERROR(X124/W124-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>부문 간 내부매출·대체</t>
+          <t>부문 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C126" s="20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D126" s="20" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="F126" s="20" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="G126" s="20" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="H126" s="20" t="n">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="K126" s="20" t="n">
-        <v>0</v>
+        <v>1528</v>
       </c>
       <c r="L126" s="20" t="n">
-        <v>0</v>
+        <v>1179</v>
       </c>
       <c r="M126" s="20" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="N126" s="20" t="n">
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W126" s="20" t="n">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="X126" s="20" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="18" t="inlineStr">
-        <is>
-          <t>부문 · 계</t>
-        </is>
-      </c>
-      <c r="C127" s="20" t="n">
-        <v>4064</v>
-      </c>
-      <c r="D127" s="20" t="n">
-        <v>3804</v>
-      </c>
-      <c r="F127" s="20" t="n">
-        <v>3341</v>
-      </c>
-      <c r="G127" s="20" t="n">
-        <v>3729</v>
-      </c>
-      <c r="H127" s="20" t="n">
-        <v>3860</v>
-      </c>
-      <c r="I127" s="20" t="n">
-        <v>5101</v>
-      </c>
-      <c r="J127" s="20" t="n">
-        <v>4019</v>
-      </c>
-      <c r="K127" s="20" t="n">
-        <v>6139</v>
-      </c>
-      <c r="L127" s="20" t="n">
-        <v>5844</v>
-      </c>
-      <c r="M127" s="20" t="n">
-        <v>7856</v>
-      </c>
-      <c r="N127" s="20" t="n">
-        <v>7240</v>
-      </c>
-      <c r="W127" s="20" t="n">
-        <v>5101</v>
-      </c>
-      <c r="X127" s="20" t="n">
-        <v>7856</v>
+      <c r="A127" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G127" s="15">
+        <f>IF(OR(G126="",C126=""),"",IF(C126&lt;=0,"",IFERROR(G126/C126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H127" s="15">
+        <f>IF(OR(H126="",D126=""),"",IF(D126&lt;=0,"",IFERROR(H126/D126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I127" s="15">
+        <f>IF(OR(I126="",E126=""),"",IF(E126&lt;=0,"",IFERROR(I126/E126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J127" s="15">
+        <f>IF(OR(J126="",F126=""),"",IF(F126&lt;=0,"",IFERROR(J126/F126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K127" s="15">
+        <f>IF(OR(K126="",G126=""),"",IF(G126&lt;=0,"",IFERROR(K126/G126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L127" s="15">
+        <f>IF(OR(L126="",H126=""),"",IF(H126&lt;=0,"",IFERROR(L126/H126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M127" s="15">
+        <f>IF(OR(M126="",I126=""),"",IF(I126&lt;=0,"",IFERROR(M126/I126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N127" s="15">
+        <f>IF(OR(N126="",J126=""),"",IF(J126&lt;=0,"",IFERROR(N126/J126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W127" s="15">
+        <f>IF(OR(W126="",V126=""),"",IF(V126&lt;=0,"",IFERROR(W126/V126-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X127" s="15">
+        <f>IF(OR(X126="",W126=""),"",IF(W126&lt;=0,"",IFERROR(X126/W126-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
-        </is>
-      </c>
-      <c r="C128" s="20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D128" s="20" t="n">
-        <v>779</v>
+          <t>보고부문 합계 · 외부 고객 매출</t>
+        </is>
       </c>
       <c r="F128" s="20" t="n">
-        <v>745</v>
+        <v>4087</v>
       </c>
       <c r="G128" s="20" t="n">
-        <v>1290</v>
+        <v>5019</v>
       </c>
       <c r="H128" s="20" t="n">
-        <v>705</v>
+        <v>4564</v>
       </c>
       <c r="I128" s="20" t="n">
-        <v>1351</v>
+        <v>6452</v>
       </c>
       <c r="J128" s="20" t="n">
-        <v>1047</v>
+        <v>5037</v>
       </c>
       <c r="K128" s="20" t="n">
-        <v>1578</v>
+        <v>7666</v>
       </c>
       <c r="L128" s="20" t="n">
-        <v>1225</v>
+        <v>7023</v>
       </c>
       <c r="M128" s="20" t="n">
-        <v>1659</v>
+        <v>9468</v>
       </c>
       <c r="N128" s="20" t="n">
-        <v>1086</v>
+        <v>8304</v>
       </c>
       <c r="W128" s="20" t="n">
-        <v>1351</v>
+        <v>6452</v>
       </c>
       <c r="X128" s="20" t="n">
-        <v>1659</v>
+        <v>9468</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · 계</t>
-        </is>
-      </c>
-      <c r="F129" s="20" t="n">
-        <v>4087</v>
-      </c>
-      <c r="G129" s="20" t="n">
-        <v>5019</v>
-      </c>
-      <c r="H129" s="20" t="n">
-        <v>4564</v>
-      </c>
-      <c r="I129" s="20" t="n">
-        <v>6452</v>
-      </c>
-      <c r="J129" s="20" t="n">
-        <v>5066</v>
-      </c>
-      <c r="K129" s="20" t="n">
-        <v>7718</v>
-      </c>
-      <c r="L129" s="20" t="n">
-        <v>7068</v>
-      </c>
-      <c r="M129" s="20" t="n">
-        <v>9515</v>
-      </c>
-      <c r="N129" s="20" t="n">
-        <v>8326</v>
-      </c>
-      <c r="W129" s="20" t="n">
-        <v>6452</v>
-      </c>
-      <c r="X129" s="20" t="n">
-        <v>9515</v>
+      <c r="A129" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G129" s="15">
+        <f>IF(OR(G128="",C128=""),"",IF(C128&lt;=0,"",IFERROR(G128/C128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H129" s="15">
+        <f>IF(OR(H128="",D128=""),"",IF(D128&lt;=0,"",IFERROR(H128/D128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I129" s="15">
+        <f>IF(OR(I128="",E128=""),"",IF(E128&lt;=0,"",IFERROR(I128/E128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J129" s="15">
+        <f>IF(OR(J128="",F128=""),"",IF(F128&lt;=0,"",IFERROR(J128/F128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K129" s="15">
+        <f>IF(OR(K128="",G128=""),"",IF(G128&lt;=0,"",IFERROR(K128/G128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L129" s="15">
+        <f>IF(OR(L128="",H128=""),"",IF(H128&lt;=0,"",IFERROR(L128/H128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M129" s="15">
+        <f>IF(OR(M128="",I128=""),"",IF(I128&lt;=0,"",IFERROR(M128/I128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N129" s="15">
+        <f>IF(OR(N128="",J128=""),"",IF(J128&lt;=0,"",IFERROR(N128/J128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W129" s="15">
+        <f>IF(OR(W128="",V128=""),"",IF(V128&lt;=0,"",IFERROR(W128/V128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X129" s="15">
+        <f>IF(OR(X128="",W128=""),"",IF(W128&lt;=0,"",IFERROR(X128/W128-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>조정액 · 계</t>
+          <t>조정액 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="F130" s="20" t="n">
@@ -8565,31 +8756,31 @@
         <v>0</v>
       </c>
       <c r="J130" s="20" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="K130" s="20" t="n">
-        <v>-51</v>
+        <v>0</v>
       </c>
       <c r="L130" s="20" t="n">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="M130" s="20" t="n">
-        <v>-47</v>
+        <v>0</v>
       </c>
       <c r="N130" s="20" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="W130" s="20" t="n">
         <v>0</v>
       </c>
       <c r="X130" s="20" t="n">
-        <v>-47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>계</t>
+          <t>외부 고객 매출</t>
         </is>
       </c>
       <c r="C131" s="12" t="n">
@@ -8633,141 +8824,153 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="18" t="inlineStr">
-        <is>
-          <t>부문 · 부문 이익</t>
-        </is>
-      </c>
-      <c r="C132" s="20" t="n">
-        <v>693</v>
-      </c>
-      <c r="D132" s="20" t="n">
-        <v>723</v>
-      </c>
-      <c r="F132" s="20" t="n">
-        <v>513</v>
-      </c>
-      <c r="G132" s="20" t="n">
-        <v>755</v>
-      </c>
-      <c r="H132" s="20" t="n">
-        <v>718</v>
-      </c>
-      <c r="I132" s="20" t="n">
-        <v>1060</v>
-      </c>
-      <c r="J132" s="20" t="n">
-        <v>554</v>
-      </c>
-      <c r="K132" s="20" t="n">
-        <v>1256</v>
-      </c>
-      <c r="L132" s="20" t="n">
-        <v>1360</v>
-      </c>
-      <c r="M132" s="20" t="n">
-        <v>1926</v>
-      </c>
-      <c r="N132" s="20" t="n">
-        <v>1742</v>
-      </c>
-      <c r="W132" s="20" t="n">
-        <v>1060</v>
-      </c>
-      <c r="X132" s="20" t="n">
-        <v>1926</v>
+      <c r="A132" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G132" s="15">
+        <f>IF(OR(G131="",C131=""),"",IF(C131&lt;=0,"",IFERROR(G131/C131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H132" s="15">
+        <f>IF(OR(H131="",D131=""),"",IF(D131&lt;=0,"",IFERROR(H131/D131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I132" s="15">
+        <f>IF(OR(I131="",E131=""),"",IF(E131&lt;=0,"",IFERROR(I131/E131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J132" s="15">
+        <f>IF(OR(J131="",F131=""),"",IF(F131&lt;=0,"",IFERROR(J131/F131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K132" s="15">
+        <f>IF(OR(K131="",G131=""),"",IF(G131&lt;=0,"",IFERROR(K131/G131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L132" s="15">
+        <f>IF(OR(L131="",H131=""),"",IF(H131&lt;=0,"",IFERROR(L131/H131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M132" s="15">
+        <f>IF(OR(M131="",I131=""),"",IF(I131&lt;=0,"",IFERROR(M131/I131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N132" s="15">
+        <f>IF(OR(N131="",J131=""),"",IF(J131&lt;=0,"",IFERROR(N131/J131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W132" s="15">
+        <f>IF(OR(W131="",V131=""),"",IF(V131&lt;=0,"",IFERROR(W131/V131-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X132" s="15">
+        <f>IF(OR(X131="",W131=""),"",IF(W131&lt;=0,"",IFERROR(X131/W131-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>부문 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C133" s="20" t="n">
-        <v>-58</v>
+        <v>0</v>
       </c>
       <c r="D133" s="20" t="n">
-        <v>-124</v>
+        <v>0</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>-188</v>
+        <v>0</v>
       </c>
       <c r="G133" s="20" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H133" s="20" t="n">
-        <v>-202</v>
+        <v>0</v>
       </c>
       <c r="I133" s="20" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K133" s="20" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="L133" s="20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M133" s="20" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="N133" s="20" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="W133" s="20" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="X133" s="20" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 부문 이익</t>
-        </is>
+          <t>부문 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="20" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="G134" s="20" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="H134" s="20" t="n">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="I134" s="20" t="n">
-        <v>1131</v>
+        <v>0</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>582</v>
+        <v>29</v>
       </c>
       <c r="K134" s="20" t="n">
-        <v>1395</v>
+        <v>51</v>
       </c>
       <c r="L134" s="20" t="n">
-        <v>1394</v>
+        <v>46</v>
       </c>
       <c r="M134" s="20" t="n">
-        <v>2144</v>
+        <v>47</v>
       </c>
       <c r="N134" s="20" t="n">
-        <v>1727</v>
+        <v>21</v>
       </c>
       <c r="W134" s="20" t="n">
-        <v>1131</v>
+        <v>0</v>
       </c>
       <c r="X134" s="20" t="n">
-        <v>2144</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>조정액 · 부문 이익</t>
+          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="F135" s="20" t="n">
@@ -8783,1680 +8986,2820 @@
         <v>0</v>
       </c>
       <c r="J135" s="20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K135" s="20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L135" s="20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N135" s="20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W135" s="20" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="20" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>부문 이익</t>
-        </is>
-      </c>
-      <c r="C136" s="12" t="n">
-        <v>635</v>
-      </c>
-      <c r="D136" s="12" t="n">
-        <v>599</v>
-      </c>
-      <c r="F136" s="12" t="n">
-        <v>325</v>
-      </c>
-      <c r="G136" s="12" t="n">
-        <v>823</v>
-      </c>
-      <c r="H136" s="12" t="n">
-        <v>517</v>
-      </c>
-      <c r="I136" s="12" t="n">
-        <v>1131</v>
-      </c>
-      <c r="J136" s="12" t="n">
-        <v>582</v>
-      </c>
-      <c r="K136" s="12" t="n">
-        <v>1395</v>
-      </c>
-      <c r="L136" s="12" t="n">
-        <v>1394</v>
-      </c>
-      <c r="M136" s="12" t="n">
-        <v>2144</v>
-      </c>
-      <c r="N136" s="12" t="n">
-        <v>1727</v>
-      </c>
-      <c r="W136" s="12" t="n">
-        <v>1131</v>
-      </c>
-      <c r="X136" s="12" t="n">
-        <v>2144</v>
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>조정액 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="F136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="20" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K136" s="20" t="n">
+        <v>-51</v>
+      </c>
+      <c r="L136" s="20" t="n">
+        <v>-46</v>
+      </c>
+      <c r="M136" s="20" t="n">
+        <v>-47</v>
+      </c>
+      <c r="N136" s="20" t="n">
+        <v>-21</v>
+      </c>
+      <c r="W136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="20" t="n">
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="C137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="16" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B138" s="42" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C138" s="16" t="n"/>
-      <c r="D138" s="16" t="n"/>
-      <c r="E138" s="16" t="n"/>
-      <c r="F138" s="16" t="n"/>
-      <c r="G138" s="16" t="n"/>
-      <c r="H138" s="16" t="n"/>
-      <c r="I138" s="16" t="n"/>
-      <c r="J138" s="16" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="16" t="n"/>
-      <c r="M138" s="16" t="n"/>
-      <c r="N138" s="16" t="n"/>
-      <c r="O138" s="16" t="n"/>
-      <c r="P138" s="16" t="n"/>
-      <c r="Q138" s="16" t="n"/>
-      <c r="R138" s="16" t="n"/>
-      <c r="S138" s="16" t="n"/>
-      <c r="T138" s="16" t="n"/>
-      <c r="U138" s="16" t="n"/>
-      <c r="V138" s="16" t="n"/>
-      <c r="W138" s="16" t="n"/>
-      <c r="X138" s="16" t="n"/>
-      <c r="Y138" s="16" t="n"/>
-      <c r="Z138" s="16" t="n"/>
-      <c r="AA138" s="16" t="n"/>
-      <c r="AB138" s="16" t="n"/>
-      <c r="AC138" s="16" t="n"/>
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>부문 · 계</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="n">
+        <v>4064</v>
+      </c>
+      <c r="D138" s="20" t="n">
+        <v>3804</v>
+      </c>
+      <c r="F138" s="20" t="n">
+        <v>3341</v>
+      </c>
+      <c r="G138" s="20" t="n">
+        <v>3729</v>
+      </c>
+      <c r="H138" s="20" t="n">
+        <v>3860</v>
+      </c>
+      <c r="I138" s="20" t="n">
+        <v>5101</v>
+      </c>
+      <c r="J138" s="20" t="n">
+        <v>4019</v>
+      </c>
+      <c r="K138" s="20" t="n">
+        <v>6139</v>
+      </c>
+      <c r="L138" s="20" t="n">
+        <v>5844</v>
+      </c>
+      <c r="M138" s="20" t="n">
+        <v>7856</v>
+      </c>
+      <c r="N138" s="20" t="n">
+        <v>7240</v>
+      </c>
+      <c r="W138" s="20" t="n">
+        <v>5101</v>
+      </c>
+      <c r="X138" s="20" t="n">
+        <v>7856</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N139" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O139" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P139" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q139" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R139" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S139" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T139" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U139" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V139" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W139" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X139" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y139" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z139" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA139" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB139" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC139" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A139" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G139" s="15">
+        <f>IF(OR(G138="",C138=""),"",IF(C138&lt;=0,"",IFERROR(G138/C138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H139" s="15">
+        <f>IF(OR(H138="",D138=""),"",IF(D138&lt;=0,"",IFERROR(H138/D138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I139" s="15">
+        <f>IF(OR(I138="",E138=""),"",IF(E138&lt;=0,"",IFERROR(I138/E138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J139" s="15">
+        <f>IF(OR(J138="",F138=""),"",IF(F138&lt;=0,"",IFERROR(J138/F138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K139" s="15">
+        <f>IF(OR(K138="",G138=""),"",IF(G138&lt;=0,"",IFERROR(K138/G138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L139" s="15">
+        <f>IF(OR(L138="",H138=""),"",IF(H138&lt;=0,"",IFERROR(L138/H138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M139" s="15">
+        <f>IF(OR(M138="",I138=""),"",IF(I138&lt;=0,"",IFERROR(M138/I138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N139" s="15">
+        <f>IF(OR(N138="",J138=""),"",IF(J138&lt;=0,"",IFERROR(N138/J138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W139" s="15">
+        <f>IF(OR(W138="",V138=""),"",IF(V138&lt;=0,"",IFERROR(W138/V138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X139" s="15">
+        <f>IF(OR(X138="",W138=""),"",IF(W138&lt;=0,"",IFERROR(X138/W138-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="n">
-        <v>2152</v>
-      </c>
-      <c r="I140" s="12" t="n">
-        <v>2710</v>
-      </c>
-      <c r="M140" s="12" t="n">
-        <v>5349</v>
-      </c>
-      <c r="O140" s="12" t="n">
-        <v>1857</v>
-      </c>
-      <c r="P140" s="12" t="n">
-        <v>597</v>
-      </c>
-      <c r="Q140" s="12" t="n">
-        <v>1657</v>
-      </c>
-      <c r="R140" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="S140" s="12" t="n">
-        <v>937</v>
-      </c>
-      <c r="T140" s="12" t="n">
-        <v>1781</v>
-      </c>
-      <c r="U140" s="12" t="n">
-        <v>2003</v>
-      </c>
-      <c r="V140" s="12" t="n">
-        <v>2152</v>
-      </c>
-      <c r="W140" s="12" t="n">
-        <v>2710</v>
-      </c>
-      <c r="X140" s="12" t="n">
-        <v>5349</v>
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>부문 · 계</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D140" s="20" t="n">
+        <v>779</v>
+      </c>
+      <c r="F140" s="20" t="n">
+        <v>745</v>
+      </c>
+      <c r="G140" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H140" s="20" t="n">
+        <v>705</v>
+      </c>
+      <c r="I140" s="20" t="n">
+        <v>1351</v>
+      </c>
+      <c r="J140" s="20" t="n">
+        <v>1047</v>
+      </c>
+      <c r="K140" s="20" t="n">
+        <v>1578</v>
+      </c>
+      <c r="L140" s="20" t="n">
+        <v>1225</v>
+      </c>
+      <c r="M140" s="20" t="n">
+        <v>1659</v>
+      </c>
+      <c r="N140" s="20" t="n">
+        <v>1086</v>
+      </c>
+      <c r="W140" s="20" t="n">
+        <v>1351</v>
+      </c>
+      <c r="X140" s="20" t="n">
+        <v>1659</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="18" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E141" s="20" t="n">
-        <v>287</v>
-      </c>
-      <c r="I141" s="20" t="n">
-        <v>478</v>
-      </c>
-      <c r="M141" s="20" t="n">
-        <v>479</v>
-      </c>
-      <c r="O141" s="20" t="n">
-        <v>473</v>
-      </c>
-      <c r="P141" s="20" t="n">
-        <v>655</v>
-      </c>
-      <c r="Q141" s="20" t="n">
-        <v>393</v>
-      </c>
-      <c r="R141" s="20" t="n">
-        <v>259</v>
-      </c>
-      <c r="S141" s="20" t="n">
-        <v>291</v>
-      </c>
-      <c r="T141" s="20" t="n">
-        <v>250</v>
-      </c>
-      <c r="U141" s="20" t="n">
-        <v>217</v>
-      </c>
-      <c r="V141" s="20" t="n">
-        <v>287</v>
-      </c>
-      <c r="W141" s="20" t="n">
-        <v>478</v>
-      </c>
-      <c r="X141" s="20" t="n">
-        <v>479</v>
+      <c r="A141" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G141" s="15">
+        <f>IF(OR(G140="",C140=""),"",IF(C140&lt;=0,"",IFERROR(G140/C140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H141" s="15">
+        <f>IF(OR(H140="",D140=""),"",IF(D140&lt;=0,"",IFERROR(H140/D140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I141" s="15">
+        <f>IF(OR(I140="",E140=""),"",IF(E140&lt;=0,"",IFERROR(I140/E140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J141" s="15">
+        <f>IF(OR(J140="",F140=""),"",IF(F140&lt;=0,"",IFERROR(J140/F140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K141" s="15">
+        <f>IF(OR(K140="",G140=""),"",IF(G140&lt;=0,"",IFERROR(K140/G140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L141" s="15">
+        <f>IF(OR(L140="",H140=""),"",IF(H140&lt;=0,"",IFERROR(L140/H140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M141" s="15">
+        <f>IF(OR(M140="",I140=""),"",IF(I140&lt;=0,"",IFERROR(M140/I140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N141" s="15">
+        <f>IF(OR(N140="",J140=""),"",IF(J140&lt;=0,"",IFERROR(N140/J140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W141" s="15">
+        <f>IF(OR(W140="",V140=""),"",IF(V140&lt;=0,"",IFERROR(W140/V140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X141" s="15">
+        <f>IF(OR(X140="",W140=""),"",IF(W140&lt;=0,"",IFERROR(X140/W140-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E142" s="20" t="n">
-        <v>-89</v>
+          <t>보고부문 합계 · 계</t>
+        </is>
+      </c>
+      <c r="F142" s="20" t="n">
+        <v>4087</v>
+      </c>
+      <c r="G142" s="20" t="n">
+        <v>5019</v>
+      </c>
+      <c r="H142" s="20" t="n">
+        <v>4564</v>
       </c>
       <c r="I142" s="20" t="n">
-        <v>71</v>
+        <v>6452</v>
+      </c>
+      <c r="J142" s="20" t="n">
+        <v>5066</v>
+      </c>
+      <c r="K142" s="20" t="n">
+        <v>7718</v>
+      </c>
+      <c r="L142" s="20" t="n">
+        <v>7068</v>
       </c>
       <c r="M142" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="O142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="Q142" s="20" t="n">
-        <v>-423</v>
-      </c>
-      <c r="R142" s="20" t="n">
-        <v>157</v>
-      </c>
-      <c r="S142" s="20" t="n">
-        <v>202</v>
-      </c>
-      <c r="T142" s="20" t="n">
-        <v>117</v>
-      </c>
-      <c r="U142" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="V142" s="20" t="n">
-        <v>-89</v>
+        <v>9515</v>
+      </c>
+      <c r="N142" s="20" t="n">
+        <v>8326</v>
       </c>
       <c r="W142" s="20" t="n">
-        <v>71</v>
+        <v>6452</v>
       </c>
       <c r="X142" s="20" t="n">
-        <v>54</v>
+        <v>9515</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="18" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="E143" s="20" t="n">
-        <v>-162</v>
-      </c>
-      <c r="I143" s="20" t="n">
-        <v>-165</v>
-      </c>
-      <c r="M143" s="20" t="n">
-        <v>-46</v>
-      </c>
-      <c r="O143" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="P143" s="20" t="n">
-        <v>-1414</v>
-      </c>
-      <c r="Q143" s="20" t="n">
-        <v>-181</v>
-      </c>
-      <c r="R143" s="20" t="n">
-        <v>-168</v>
-      </c>
-      <c r="S143" s="20" t="n">
-        <v>-554</v>
-      </c>
-      <c r="T143" s="20" t="n">
-        <v>-127</v>
-      </c>
-      <c r="U143" s="20" t="n">
-        <v>-144</v>
-      </c>
-      <c r="V143" s="20" t="n">
-        <v>-162</v>
-      </c>
-      <c r="W143" s="20" t="n">
-        <v>-165</v>
-      </c>
-      <c r="X143" s="20" t="n">
-        <v>-46</v>
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G143" s="15">
+        <f>IF(OR(G142="",C142=""),"",IF(C142&lt;=0,"",IFERROR(G142/C142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H143" s="15">
+        <f>IF(OR(H142="",D142=""),"",IF(D142&lt;=0,"",IFERROR(H142/D142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I143" s="15">
+        <f>IF(OR(I142="",E142=""),"",IF(E142&lt;=0,"",IFERROR(I142/E142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J143" s="15">
+        <f>IF(OR(J142="",F142=""),"",IF(F142&lt;=0,"",IFERROR(J142/F142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K143" s="15">
+        <f>IF(OR(K142="",G142=""),"",IF(G142&lt;=0,"",IFERROR(K142/G142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L143" s="15">
+        <f>IF(OR(L142="",H142=""),"",IF(H142&lt;=0,"",IFERROR(L142/H142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M143" s="15">
+        <f>IF(OR(M142="",I142=""),"",IF(I142&lt;=0,"",IFERROR(M142/I142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N143" s="15">
+        <f>IF(OR(N142="",J142=""),"",IF(J142&lt;=0,"",IFERROR(N142/J142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W143" s="15">
+        <f>IF(OR(W142="",V142=""),"",IF(V142&lt;=0,"",IFERROR(W142/V142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X143" s="15">
+        <f>IF(OR(X142="",W142=""),"",IF(W142&lt;=0,"",IFERROR(X142/W142-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>퇴직급여자산 증감</t>
-        </is>
-      </c>
-      <c r="E144" s="20" t="n">
-        <v>-88</v>
+          <t>조정액 · 계</t>
+        </is>
+      </c>
+      <c r="F144" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="I144" s="20" t="n">
-        <v>-96</v>
+        <v>0</v>
+      </c>
+      <c r="J144" s="20" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K144" s="20" t="n">
+        <v>-51</v>
+      </c>
+      <c r="L144" s="20" t="n">
+        <v>-46</v>
       </c>
       <c r="M144" s="20" t="n">
-        <v>-94</v>
-      </c>
-      <c r="O144" s="20" t="n">
-        <v>-118</v>
-      </c>
-      <c r="P144" s="20" t="n">
-        <v>-78</v>
-      </c>
-      <c r="Q144" s="20" t="n">
-        <v>-118</v>
-      </c>
-      <c r="R144" s="20" t="n">
-        <v>-224</v>
-      </c>
-      <c r="S144" s="20" t="n">
-        <v>-122</v>
-      </c>
-      <c r="T144" s="20" t="n">
-        <v>-92</v>
-      </c>
-      <c r="U144" s="20" t="n">
-        <v>-97</v>
-      </c>
-      <c r="V144" s="20" t="n">
-        <v>-88</v>
+        <v>-47</v>
+      </c>
+      <c r="N144" s="20" t="n">
+        <v>-21</v>
       </c>
       <c r="W144" s="20" t="n">
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="X144" s="20" t="n">
-        <v>-94</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="18" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="E145" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I145" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M145" s="20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="R145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="S145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U145" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V145" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W145" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X145" s="20" t="n">
-        <v>-3</v>
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="n">
+        <v>5064</v>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>4584</v>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>4087</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>5019</v>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>4564</v>
+      </c>
+      <c r="I145" s="12" t="n">
+        <v>6452</v>
+      </c>
+      <c r="J145" s="12" t="n">
+        <v>5037</v>
+      </c>
+      <c r="K145" s="12" t="n">
+        <v>7666</v>
+      </c>
+      <c r="L145" s="12" t="n">
+        <v>7023</v>
+      </c>
+      <c r="M145" s="12" t="n">
+        <v>9468</v>
+      </c>
+      <c r="N145" s="12" t="n">
+        <v>8304</v>
+      </c>
+      <c r="W145" s="12" t="n">
+        <v>6452</v>
+      </c>
+      <c r="X145" s="12" t="n">
+        <v>9468</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="18" t="inlineStr">
-        <is>
-          <t>Gain On Revision Of Retirement Benefit Plan Ope CF</t>
-        </is>
-      </c>
-      <c r="O146" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" s="20" t="n">
-        <v>-119</v>
-      </c>
-      <c r="Q146" s="20" t="n">
-        <v>0</v>
+      <c r="A146" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G146" s="15">
+        <f>IF(OR(G145="",C145=""),"",IF(C145&lt;=0,"",IFERROR(G145/C145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H146" s="15">
+        <f>IF(OR(H145="",D145=""),"",IF(D145&lt;=0,"",IFERROR(H145/D145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I146" s="15">
+        <f>IF(OR(I145="",E145=""),"",IF(E145&lt;=0,"",IFERROR(I145/E145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J146" s="15">
+        <f>IF(OR(J145="",F145=""),"",IF(F145&lt;=0,"",IFERROR(J145/F145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K146" s="15">
+        <f>IF(OR(K145="",G145=""),"",IF(G145&lt;=0,"",IFERROR(K145/G145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L146" s="15">
+        <f>IF(OR(L145="",H145=""),"",IF(H145&lt;=0,"",IFERROR(L145/H145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M146" s="15">
+        <f>IF(OR(M145="",I145=""),"",IF(I145&lt;=0,"",IFERROR(M145/I145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N146" s="15">
+        <f>IF(OR(N145="",J145=""),"",IF(J145&lt;=0,"",IFERROR(N145/J145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W146" s="15">
+        <f>IF(OR(W145="",V145=""),"",IF(V145&lt;=0,"",IFERROR(W145/V145-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X146" s="15">
+        <f>IF(OR(X145="",W145=""),"",IF(W145&lt;=0,"",IFERROR(X145/W145-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="E147" s="20" t="n">
-        <v>29</v>
+          <t>부문 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C147" s="20" t="n">
+        <v>693</v>
+      </c>
+      <c r="D147" s="20" t="n">
+        <v>723</v>
+      </c>
+      <c r="F147" s="20" t="n">
+        <v>513</v>
+      </c>
+      <c r="G147" s="20" t="n">
+        <v>755</v>
+      </c>
+      <c r="H147" s="20" t="n">
+        <v>718</v>
       </c>
       <c r="I147" s="20" t="n">
-        <v>47</v>
+        <v>1060</v>
+      </c>
+      <c r="J147" s="20" t="n">
+        <v>554</v>
+      </c>
+      <c r="K147" s="20" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L147" s="20" t="n">
+        <v>1360</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>104</v>
-      </c>
-      <c r="O147" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="P147" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q147" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="R147" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="S147" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="T147" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="U147" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="V147" s="20" t="n">
-        <v>29</v>
+        <v>1926</v>
+      </c>
+      <c r="N147" s="20" t="n">
+        <v>1742</v>
       </c>
       <c r="W147" s="20" t="n">
-        <v>47</v>
+        <v>1060</v>
       </c>
       <c r="X147" s="20" t="n">
-        <v>104</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="18" t="inlineStr">
-        <is>
-          <t>보상금 수취</t>
-        </is>
-      </c>
-      <c r="O148" s="20" t="n">
-        <v>-3694</v>
-      </c>
-      <c r="P148" s="20" t="n">
-        <v>-1477</v>
-      </c>
-      <c r="Q148" s="20" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="R148" s="20" t="n">
-        <v>0</v>
+      <c r="A148" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C148" s="15">
+        <f>IF(OR(C147="",C138=""),"",IF(C138&lt;=0,"",IFERROR(C147/C138,"")))</f>
+        <v/>
+      </c>
+      <c r="D148" s="15">
+        <f>IF(OR(D147="",D138=""),"",IF(D138&lt;=0,"",IFERROR(D147/D138,"")))</f>
+        <v/>
+      </c>
+      <c r="F148" s="15">
+        <f>IF(OR(F147="",F138=""),"",IF(F138&lt;=0,"",IFERROR(F147/F138,"")))</f>
+        <v/>
+      </c>
+      <c r="G148" s="15">
+        <f>IF(OR(G147="",G138=""),"",IF(G138&lt;=0,"",IFERROR(G147/G138,"")))</f>
+        <v/>
+      </c>
+      <c r="H148" s="15">
+        <f>IF(OR(H147="",H138=""),"",IF(H138&lt;=0,"",IFERROR(H147/H138,"")))</f>
+        <v/>
+      </c>
+      <c r="I148" s="15">
+        <f>IF(OR(I147="",I138=""),"",IF(I138&lt;=0,"",IFERROR(I147/I138,"")))</f>
+        <v/>
+      </c>
+      <c r="J148" s="15">
+        <f>IF(OR(J147="",J138=""),"",IF(J138&lt;=0,"",IFERROR(J147/J138,"")))</f>
+        <v/>
+      </c>
+      <c r="K148" s="15">
+        <f>IF(OR(K147="",K138=""),"",IF(K138&lt;=0,"",IFERROR(K147/K138,"")))</f>
+        <v/>
+      </c>
+      <c r="L148" s="15">
+        <f>IF(OR(L147="",L138=""),"",IF(L138&lt;=0,"",IFERROR(L147/L138,"")))</f>
+        <v/>
+      </c>
+      <c r="M148" s="15">
+        <f>IF(OR(M147="",M138=""),"",IF(M138&lt;=0,"",IFERROR(M147/M138,"")))</f>
+        <v/>
+      </c>
+      <c r="N148" s="15">
+        <f>IF(OR(N147="",N138=""),"",IF(N138&lt;=0,"",IFERROR(N147/N138,"")))</f>
+        <v/>
+      </c>
+      <c r="W148" s="15">
+        <f>IF(OR(W147="",W138=""),"",IF(W138&lt;=0,"",IFERROR(W147/W138,"")))</f>
+        <v/>
+      </c>
+      <c r="X148" s="15">
+        <f>IF(OR(X147="",X138=""),"",IF(X138&lt;=0,"",IFERROR(X147/X138,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="18" t="inlineStr">
-        <is>
-          <t>Loss On Business Transfer Ope CF</t>
-        </is>
-      </c>
-      <c r="O149" s="20" t="n">
-        <v>1775</v>
-      </c>
-      <c r="P149" s="20" t="n">
-        <v>231</v>
-      </c>
-      <c r="Q149" s="20" t="n">
-        <v>0</v>
+      <c r="A149" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G149" s="15">
+        <f>IF(OR(G147="",C147=""),"",IF(C147&lt;=0,"",IFERROR(G147/C147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H149" s="15">
+        <f>IF(OR(H147="",D147=""),"",IF(D147&lt;=0,"",IFERROR(H147/D147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I149" s="15">
+        <f>IF(OR(I147="",E147=""),"",IF(E147&lt;=0,"",IFERROR(I147/E147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J149" s="15">
+        <f>IF(OR(J147="",F147=""),"",IF(F147&lt;=0,"",IFERROR(J147/F147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K149" s="15">
+        <f>IF(OR(K147="",G147=""),"",IF(G147&lt;=0,"",IFERROR(K147/G147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L149" s="15">
+        <f>IF(OR(L147="",H147=""),"",IF(H147&lt;=0,"",IFERROR(L147/H147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M149" s="15">
+        <f>IF(OR(M147="",I147=""),"",IF(I147&lt;=0,"",IFERROR(M147/I147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N149" s="15">
+        <f>IF(OR(N147="",J147=""),"",IF(J147&lt;=0,"",IFERROR(N147/J147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W149" s="15">
+        <f>IF(OR(W147="",V147=""),"",IF(V147&lt;=0,"",IFERROR(W147/V147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X149" s="15">
+        <f>IF(OR(X147="",W147=""),"",IF(W147&lt;=0,"",IFERROR(X147/W147-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>Decrease In Loss On Business Transfer Ope CF</t>
-        </is>
-      </c>
-      <c r="O150" s="20" t="n">
-        <v>-49</v>
-      </c>
-      <c r="P150" s="20" t="n">
-        <v>-1041</v>
-      </c>
-      <c r="Q150" s="20" t="n">
-        <v>-836</v>
-      </c>
-      <c r="R150" s="20" t="n">
-        <v>-82</v>
-      </c>
-      <c r="S150" s="20" t="n">
-        <v>0</v>
+          <t>부문 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C150" s="20" t="n">
+        <v>-58</v>
+      </c>
+      <c r="D150" s="20" t="n">
+        <v>-124</v>
+      </c>
+      <c r="F150" s="20" t="n">
+        <v>-188</v>
+      </c>
+      <c r="G150" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="H150" s="20" t="n">
+        <v>-202</v>
+      </c>
+      <c r="I150" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="J150" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="K150" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="L150" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="M150" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="N150" s="20" t="n">
+        <v>-15</v>
+      </c>
+      <c r="W150" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="X150" s="20" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="18" t="inlineStr">
-        <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="O151" s="20" t="n">
-        <v>-42</v>
-      </c>
-      <c r="P151" s="20" t="n">
-        <v>365</v>
-      </c>
-      <c r="Q151" s="20" t="n">
-        <v>-579</v>
-      </c>
-      <c r="R151" s="20" t="n">
-        <v>775</v>
-      </c>
-      <c r="S151" s="20" t="n">
-        <v>-311</v>
-      </c>
-      <c r="T151" s="20" t="n">
-        <v>2205</v>
+      <c r="A151" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C151" s="15">
+        <f>IF(OR(C150="",C140=""),"",IF(C140&lt;=0,"",IFERROR(C150/C140,"")))</f>
+        <v/>
+      </c>
+      <c r="D151" s="15">
+        <f>IF(OR(D150="",D140=""),"",IF(D140&lt;=0,"",IFERROR(D150/D140,"")))</f>
+        <v/>
+      </c>
+      <c r="F151" s="15">
+        <f>IF(OR(F150="",F140=""),"",IF(F140&lt;=0,"",IFERROR(F150/F140,"")))</f>
+        <v/>
+      </c>
+      <c r="G151" s="15">
+        <f>IF(OR(G150="",G140=""),"",IF(G140&lt;=0,"",IFERROR(G150/G140,"")))</f>
+        <v/>
+      </c>
+      <c r="H151" s="15">
+        <f>IF(OR(H150="",H140=""),"",IF(H140&lt;=0,"",IFERROR(H150/H140,"")))</f>
+        <v/>
+      </c>
+      <c r="I151" s="15">
+        <f>IF(OR(I150="",I140=""),"",IF(I140&lt;=0,"",IFERROR(I150/I140,"")))</f>
+        <v/>
+      </c>
+      <c r="J151" s="15">
+        <f>IF(OR(J150="",J140=""),"",IF(J140&lt;=0,"",IFERROR(J150/J140,"")))</f>
+        <v/>
+      </c>
+      <c r="K151" s="15">
+        <f>IF(OR(K150="",K140=""),"",IF(K140&lt;=0,"",IFERROR(K150/K140,"")))</f>
+        <v/>
+      </c>
+      <c r="L151" s="15">
+        <f>IF(OR(L150="",L140=""),"",IF(L140&lt;=0,"",IFERROR(L150/L140,"")))</f>
+        <v/>
+      </c>
+      <c r="M151" s="15">
+        <f>IF(OR(M150="",M140=""),"",IF(M140&lt;=0,"",IFERROR(M150/M140,"")))</f>
+        <v/>
+      </c>
+      <c r="N151" s="15">
+        <f>IF(OR(N150="",N140=""),"",IF(N140&lt;=0,"",IFERROR(N150/N140,"")))</f>
+        <v/>
+      </c>
+      <c r="W151" s="15">
+        <f>IF(OR(W150="",W140=""),"",IF(W140&lt;=0,"",IFERROR(W150/W140,"")))</f>
+        <v/>
+      </c>
+      <c r="X151" s="15">
+        <f>IF(OR(X150="",X140=""),"",IF(X140&lt;=0,"",IFERROR(X150/X140,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="18" t="inlineStr">
-        <is>
-          <t>Loss Gain On Sales Of Land Ope CF</t>
-        </is>
-      </c>
-      <c r="E152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" s="20" t="n">
-        <v>-83</v>
-      </c>
-      <c r="V152" s="20" t="n">
-        <v>0</v>
+      <c r="A152" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G152" s="15">
+        <f>IF(OR(G150="",C150=""),"",IF(C150&lt;=0,"",IFERROR(G150/C150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H152" s="15">
+        <f>IF(OR(H150="",D150=""),"",IF(D150&lt;=0,"",IFERROR(H150/D150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I152" s="15">
+        <f>IF(OR(I150="",E150=""),"",IF(E150&lt;=0,"",IFERROR(I150/E150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J152" s="15">
+        <f>IF(OR(J150="",F150=""),"",IF(F150&lt;=0,"",IFERROR(J150/F150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K152" s="15">
+        <f>IF(OR(K150="",G150=""),"",IF(G150&lt;=0,"",IFERROR(K150/G150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L152" s="15">
+        <f>IF(OR(L150="",H150=""),"",IF(H150&lt;=0,"",IFERROR(L150/H150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M152" s="15">
+        <f>IF(OR(M150="",I150=""),"",IF(I150&lt;=0,"",IFERROR(M150/I150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N152" s="15">
+        <f>IF(OR(N150="",J150=""),"",IF(J150&lt;=0,"",IFERROR(N150/J150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W152" s="15">
+        <f>IF(OR(W150="",V150=""),"",IF(V150&lt;=0,"",IFERROR(W150/V150-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X152" s="15">
+        <f>IF(OR(X150="",W150=""),"",IF(W150&lt;=0,"",IFERROR(X150/W150-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="T153" s="20" t="n">
-        <v>2205</v>
-      </c>
-      <c r="U153" s="20" t="n">
-        <v>-2254</v>
+          <t>보고부문 합계 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="F153" s="20" t="n">
+        <v>325</v>
+      </c>
+      <c r="G153" s="20" t="n">
+        <v>823</v>
+      </c>
+      <c r="H153" s="20" t="n">
+        <v>517</v>
+      </c>
+      <c r="I153" s="20" t="n">
+        <v>1131</v>
+      </c>
+      <c r="J153" s="20" t="n">
+        <v>582</v>
+      </c>
+      <c r="K153" s="20" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L153" s="20" t="n">
+        <v>1394</v>
+      </c>
+      <c r="M153" s="20" t="n">
+        <v>2144</v>
+      </c>
+      <c r="N153" s="20" t="n">
+        <v>1727</v>
+      </c>
+      <c r="W153" s="20" t="n">
+        <v>1131</v>
+      </c>
+      <c r="X153" s="20" t="n">
+        <v>2144</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="18" t="inlineStr">
-        <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="E154" s="20" t="n">
-        <v>-1932</v>
-      </c>
-      <c r="I154" s="20" t="n">
-        <v>797</v>
-      </c>
-      <c r="M154" s="20" t="n">
-        <v>-8230</v>
-      </c>
-      <c r="U154" s="20" t="n">
-        <v>-2254</v>
-      </c>
-      <c r="V154" s="20" t="n">
-        <v>-1932</v>
-      </c>
-      <c r="W154" s="20" t="n">
-        <v>797</v>
-      </c>
-      <c r="X154" s="20" t="n">
-        <v>-8230</v>
+      <c r="A154" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="F154" s="15">
+        <f>IF(OR(F153="",F142=""),"",IF(F142&lt;=0,"",IFERROR(F153/F142,"")))</f>
+        <v/>
+      </c>
+      <c r="G154" s="15">
+        <f>IF(OR(G153="",G142=""),"",IF(G142&lt;=0,"",IFERROR(G153/G142,"")))</f>
+        <v/>
+      </c>
+      <c r="H154" s="15">
+        <f>IF(OR(H153="",H142=""),"",IF(H142&lt;=0,"",IFERROR(H153/H142,"")))</f>
+        <v/>
+      </c>
+      <c r="I154" s="15">
+        <f>IF(OR(I153="",I142=""),"",IF(I142&lt;=0,"",IFERROR(I153/I142,"")))</f>
+        <v/>
+      </c>
+      <c r="J154" s="15">
+        <f>IF(OR(J153="",J142=""),"",IF(J142&lt;=0,"",IFERROR(J153/J142,"")))</f>
+        <v/>
+      </c>
+      <c r="K154" s="15">
+        <f>IF(OR(K153="",K142=""),"",IF(K142&lt;=0,"",IFERROR(K153/K142,"")))</f>
+        <v/>
+      </c>
+      <c r="L154" s="15">
+        <f>IF(OR(L153="",L142=""),"",IF(L142&lt;=0,"",IFERROR(L153/L142,"")))</f>
+        <v/>
+      </c>
+      <c r="M154" s="15">
+        <f>IF(OR(M153="",M142=""),"",IF(M142&lt;=0,"",IFERROR(M153/M142,"")))</f>
+        <v/>
+      </c>
+      <c r="N154" s="15">
+        <f>IF(OR(N153="",N142=""),"",IF(N142&lt;=0,"",IFERROR(N153/N142,"")))</f>
+        <v/>
+      </c>
+      <c r="W154" s="15">
+        <f>IF(OR(W153="",W142=""),"",IF(W142&lt;=0,"",IFERROR(W153/W142,"")))</f>
+        <v/>
+      </c>
+      <c r="X154" s="15">
+        <f>IF(OR(X153="",X142=""),"",IF(X142&lt;=0,"",IFERROR(X153/X142,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="18" t="inlineStr">
-        <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="E155" s="20" t="n">
-        <v>-426</v>
-      </c>
-      <c r="I155" s="20" t="n">
-        <v>-420</v>
-      </c>
-      <c r="M155" s="20" t="n">
-        <v>-647</v>
-      </c>
-      <c r="O155" s="20" t="n">
-        <v>-89</v>
-      </c>
-      <c r="P155" s="20" t="n">
-        <v>-311</v>
-      </c>
-      <c r="Q155" s="20" t="n">
-        <v>770</v>
-      </c>
-      <c r="R155" s="20" t="n">
-        <v>69</v>
-      </c>
-      <c r="S155" s="20" t="n">
-        <v>-490</v>
-      </c>
-      <c r="T155" s="20" t="n">
-        <v>665</v>
-      </c>
-      <c r="U155" s="20" t="n">
-        <v>-192</v>
-      </c>
-      <c r="V155" s="20" t="n">
-        <v>-426</v>
-      </c>
-      <c r="W155" s="20" t="n">
-        <v>-420</v>
-      </c>
-      <c r="X155" s="20" t="n">
-        <v>-647</v>
+      <c r="A155" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G155" s="15">
+        <f>IF(OR(G153="",C153=""),"",IF(C153&lt;=0,"",IFERROR(G153/C153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H155" s="15">
+        <f>IF(OR(H153="",D153=""),"",IF(D153&lt;=0,"",IFERROR(H153/D153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I155" s="15">
+        <f>IF(OR(I153="",E153=""),"",IF(E153&lt;=0,"",IFERROR(I153/E153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J155" s="15">
+        <f>IF(OR(J153="",F153=""),"",IF(F153&lt;=0,"",IFERROR(J153/F153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K155" s="15">
+        <f>IF(OR(K153="",G153=""),"",IF(G153&lt;=0,"",IFERROR(K153/G153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L155" s="15">
+        <f>IF(OR(L153="",H153=""),"",IF(H153&lt;=0,"",IFERROR(L153/H153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M155" s="15">
+        <f>IF(OR(M153="",I153=""),"",IF(I153&lt;=0,"",IFERROR(M153/I153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N155" s="15">
+        <f>IF(OR(N153="",J153=""),"",IF(J153&lt;=0,"",IFERROR(N153/J153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W155" s="15">
+        <f>IF(OR(W153="",V153=""),"",IF(V153&lt;=0,"",IFERROR(W153/V153-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X155" s="15">
+        <f>IF(OR(X153="",W153=""),"",IF(W153&lt;=0,"",IFERROR(X153/W153-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="E156" s="20" t="n">
-        <v>-340</v>
+          <t>조정액 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="F156" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="I156" s="20" t="n">
-        <v>-396</v>
+        <v>0</v>
+      </c>
+      <c r="J156" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="M156" s="20" t="n">
-        <v>933</v>
-      </c>
-      <c r="O156" s="20" t="n">
-        <v>392</v>
-      </c>
-      <c r="P156" s="20" t="n">
-        <v>-487</v>
-      </c>
-      <c r="Q156" s="20" t="n">
-        <v>182</v>
-      </c>
-      <c r="R156" s="20" t="n">
-        <v>-497</v>
-      </c>
-      <c r="S156" s="20" t="n">
-        <v>839</v>
-      </c>
-      <c r="T156" s="20" t="n">
-        <v>-709</v>
-      </c>
-      <c r="U156" s="20" t="n">
-        <v>523</v>
-      </c>
-      <c r="V156" s="20" t="n">
-        <v>-340</v>
+        <v>0</v>
+      </c>
+      <c r="N156" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="W156" s="20" t="n">
-        <v>-396</v>
+        <v>0</v>
       </c>
       <c r="X156" s="20" t="n">
-        <v>933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="18" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E157" s="20" t="n">
-        <v>641</v>
-      </c>
-      <c r="I157" s="20" t="n">
-        <v>-457</v>
-      </c>
-      <c r="M157" s="20" t="n">
-        <v>-343</v>
-      </c>
-      <c r="O157" s="20" t="n">
-        <v>-171</v>
-      </c>
-      <c r="P157" s="20" t="n">
-        <v>983</v>
-      </c>
-      <c r="Q157" s="20" t="n">
-        <v>1659</v>
-      </c>
-      <c r="R157" s="20" t="n">
-        <v>-1454</v>
-      </c>
-      <c r="S157" s="20" t="n">
-        <v>104</v>
-      </c>
-      <c r="T157" s="20" t="n">
-        <v>-717</v>
-      </c>
-      <c r="U157" s="20" t="n">
-        <v>-503</v>
-      </c>
-      <c r="V157" s="20" t="n">
-        <v>641</v>
-      </c>
-      <c r="W157" s="20" t="n">
-        <v>-457</v>
-      </c>
-      <c r="X157" s="20" t="n">
-        <v>-343</v>
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>부문 이익</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="D157" s="12" t="n">
+        <v>599</v>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>325</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>823</v>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>517</v>
+      </c>
+      <c r="I157" s="12" t="n">
+        <v>1131</v>
+      </c>
+      <c r="J157" s="12" t="n">
+        <v>582</v>
+      </c>
+      <c r="K157" s="12" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L157" s="12" t="n">
+        <v>1394</v>
+      </c>
+      <c r="M157" s="12" t="n">
+        <v>2144</v>
+      </c>
+      <c r="N157" s="12" t="n">
+        <v>1727</v>
+      </c>
+      <c r="W157" s="12" t="n">
+        <v>1131</v>
+      </c>
+      <c r="X157" s="12" t="n">
+        <v>2144</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="18" t="inlineStr">
-        <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="E158" s="20" t="n">
-        <v>69</v>
-      </c>
-      <c r="I158" s="20" t="n">
-        <v>2568</v>
-      </c>
-      <c r="M158" s="20" t="n">
-        <v>-2443</v>
-      </c>
-      <c r="O158" s="20" t="n">
-        <v>426</v>
-      </c>
-      <c r="P158" s="20" t="n">
-        <v>-2070</v>
-      </c>
-      <c r="Q158" s="20" t="n">
-        <v>185</v>
-      </c>
-      <c r="R158" s="20" t="n">
-        <v>-1050</v>
-      </c>
-      <c r="S158" s="20" t="n">
-        <v>944</v>
-      </c>
-      <c r="T158" s="20" t="n">
-        <v>3410</v>
-      </c>
-      <c r="U158" s="20" t="n">
-        <v>-497</v>
-      </c>
-      <c r="V158" s="20" t="n">
-        <v>69</v>
-      </c>
-      <c r="W158" s="20" t="n">
-        <v>2568</v>
-      </c>
-      <c r="X158" s="20" t="n">
-        <v>-2443</v>
+      <c r="A158" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C158" s="15">
+        <f>IF(OR(C157="",C131=""),"",IF(C131&lt;=0,"",IFERROR(C157/C131,"")))</f>
+        <v/>
+      </c>
+      <c r="D158" s="15">
+        <f>IF(OR(D157="",D131=""),"",IF(D131&lt;=0,"",IFERROR(D157/D131,"")))</f>
+        <v/>
+      </c>
+      <c r="F158" s="15">
+        <f>IF(OR(F157="",F131=""),"",IF(F131&lt;=0,"",IFERROR(F157/F131,"")))</f>
+        <v/>
+      </c>
+      <c r="G158" s="15">
+        <f>IF(OR(G157="",G131=""),"",IF(G131&lt;=0,"",IFERROR(G157/G131,"")))</f>
+        <v/>
+      </c>
+      <c r="H158" s="15">
+        <f>IF(OR(H157="",H131=""),"",IF(H131&lt;=0,"",IFERROR(H157/H131,"")))</f>
+        <v/>
+      </c>
+      <c r="I158" s="15">
+        <f>IF(OR(I157="",I131=""),"",IF(I131&lt;=0,"",IFERROR(I157/I131,"")))</f>
+        <v/>
+      </c>
+      <c r="J158" s="15">
+        <f>IF(OR(J157="",J131=""),"",IF(J131&lt;=0,"",IFERROR(J157/J131,"")))</f>
+        <v/>
+      </c>
+      <c r="K158" s="15">
+        <f>IF(OR(K157="",K131=""),"",IF(K131&lt;=0,"",IFERROR(K157/K131,"")))</f>
+        <v/>
+      </c>
+      <c r="L158" s="15">
+        <f>IF(OR(L157="",L131=""),"",IF(L131&lt;=0,"",IFERROR(L157/L131,"")))</f>
+        <v/>
+      </c>
+      <c r="M158" s="15">
+        <f>IF(OR(M157="",M131=""),"",IF(M131&lt;=0,"",IFERROR(M157/M131,"")))</f>
+        <v/>
+      </c>
+      <c r="N158" s="15">
+        <f>IF(OR(N157="",N131=""),"",IF(N131&lt;=0,"",IFERROR(N157/N131,"")))</f>
+        <v/>
+      </c>
+      <c r="W158" s="15">
+        <f>IF(OR(W157="",W131=""),"",IF(W131&lt;=0,"",IFERROR(W157/W131,"")))</f>
+        <v/>
+      </c>
+      <c r="X158" s="15">
+        <f>IF(OR(X157="",X131=""),"",IF(X131&lt;=0,"",IFERROR(X157/X131,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="18" t="inlineStr">
-        <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="E159" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I159" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M159" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W159" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="X159" s="20" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="18" t="inlineStr">
-        <is>
-          <t>이자 지급</t>
-        </is>
-      </c>
-      <c r="E160" s="20" t="n">
-        <v>-29</v>
-      </c>
-      <c r="I160" s="20" t="n">
-        <v>-45</v>
-      </c>
-      <c r="M160" s="20" t="n">
-        <v>-103</v>
-      </c>
-      <c r="O160" s="20" t="n">
-        <v>-73</v>
-      </c>
-      <c r="P160" s="20" t="n">
-        <v>-56</v>
-      </c>
-      <c r="Q160" s="20" t="n">
-        <v>-67</v>
-      </c>
-      <c r="R160" s="20" t="n">
-        <v>-51</v>
-      </c>
-      <c r="S160" s="20" t="n">
-        <v>-49</v>
-      </c>
-      <c r="T160" s="20" t="n">
-        <v>-40</v>
-      </c>
-      <c r="U160" s="20" t="n">
-        <v>-25</v>
-      </c>
-      <c r="V160" s="20" t="n">
-        <v>-29</v>
-      </c>
-      <c r="W160" s="20" t="n">
-        <v>-45</v>
-      </c>
-      <c r="X160" s="20" t="n">
-        <v>-103</v>
+      <c r="A159" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G159" s="15">
+        <f>IF(OR(G157="",C157=""),"",IF(C157&lt;=0,"",IFERROR(G157/C157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H159" s="15">
+        <f>IF(OR(H157="",D157=""),"",IF(D157&lt;=0,"",IFERROR(H157/D157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I159" s="15">
+        <f>IF(OR(I157="",E157=""),"",IF(E157&lt;=0,"",IFERROR(I157/E157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J159" s="15">
+        <f>IF(OR(J157="",F157=""),"",IF(F157&lt;=0,"",IFERROR(J157/F157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K159" s="15">
+        <f>IF(OR(K157="",G157=""),"",IF(G157&lt;=0,"",IFERROR(K157/G157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L159" s="15">
+        <f>IF(OR(L157="",H157=""),"",IF(H157&lt;=0,"",IFERROR(L157/H157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M159" s="15">
+        <f>IF(OR(M157="",I157=""),"",IF(I157&lt;=0,"",IFERROR(M157/I157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N159" s="15">
+        <f>IF(OR(N157="",J157=""),"",IF(J157&lt;=0,"",IFERROR(N157/J157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W159" s="15">
+        <f>IF(OR(W157="",V157=""),"",IF(V157&lt;=0,"",IFERROR(W157/V157-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X159" s="15">
+        <f>IF(OR(X157="",W157=""),"",IF(W157&lt;=0,"",IFERROR(X157/W157-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="18" t="inlineStr">
-        <is>
-          <t>보상금 수취</t>
-        </is>
-      </c>
-      <c r="O161" s="20" t="n">
-        <v>3694</v>
-      </c>
-      <c r="P161" s="20" t="n">
-        <v>1477</v>
-      </c>
-      <c r="Q161" s="20" t="n">
-        <v>2400</v>
-      </c>
-      <c r="R161" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B161" s="42" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="n"/>
+      <c r="D161" s="16" t="n"/>
+      <c r="E161" s="16" t="n"/>
+      <c r="F161" s="16" t="n"/>
+      <c r="G161" s="16" t="n"/>
+      <c r="H161" s="16" t="n"/>
+      <c r="I161" s="16" t="n"/>
+      <c r="J161" s="16" t="n"/>
+      <c r="K161" s="16" t="n"/>
+      <c r="L161" s="16" t="n"/>
+      <c r="M161" s="16" t="n"/>
+      <c r="N161" s="16" t="n"/>
+      <c r="O161" s="16" t="n"/>
+      <c r="P161" s="16" t="n"/>
+      <c r="Q161" s="16" t="n"/>
+      <c r="R161" s="16" t="n"/>
+      <c r="S161" s="16" t="n"/>
+      <c r="T161" s="16" t="n"/>
+      <c r="U161" s="16" t="n"/>
+      <c r="V161" s="16" t="n"/>
+      <c r="W161" s="16" t="n"/>
+      <c r="X161" s="16" t="n"/>
+      <c r="Y161" s="16" t="n"/>
+      <c r="Z161" s="16" t="n"/>
+      <c r="AA161" s="16" t="n"/>
+      <c r="AB161" s="16" t="n"/>
+      <c r="AC161" s="16" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="18" t="inlineStr">
-        <is>
-          <t>법인세 납부</t>
-        </is>
-      </c>
-      <c r="O162" s="20" t="n">
-        <v>-17</v>
-      </c>
-      <c r="P162" s="20" t="n">
-        <v>-788</v>
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M162" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N162" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O162" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P162" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q162" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R162" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T162" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U162" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V162" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W162" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X162" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y162" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z162" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA162" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB162" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC162" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="18" t="inlineStr">
-        <is>
-          <t>법인세 납부·환급</t>
-        </is>
-      </c>
-      <c r="E163" s="20" t="n">
-        <v>-247</v>
-      </c>
-      <c r="I163" s="20" t="n">
-        <v>-374</v>
-      </c>
-      <c r="M163" s="20" t="n">
-        <v>-1077</v>
-      </c>
-      <c r="P163" s="20" t="n">
-        <v>-788</v>
-      </c>
-      <c r="Q163" s="20" t="n">
-        <v>218</v>
-      </c>
-      <c r="R163" s="20" t="n">
-        <v>-21</v>
-      </c>
-      <c r="S163" s="20" t="n">
-        <v>-35</v>
-      </c>
-      <c r="T163" s="20" t="n">
-        <v>-17</v>
-      </c>
-      <c r="U163" s="20" t="n">
-        <v>-338</v>
-      </c>
-      <c r="V163" s="20" t="n">
-        <v>-247</v>
-      </c>
-      <c r="W163" s="20" t="n">
-        <v>-374</v>
-      </c>
-      <c r="X163" s="20" t="n">
-        <v>-1077</v>
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>2152</v>
+      </c>
+      <c r="I163" s="12" t="n">
+        <v>2710</v>
+      </c>
+      <c r="M163" s="12" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O163" s="12" t="n">
+        <v>1857</v>
+      </c>
+      <c r="P163" s="12" t="n">
+        <v>597</v>
+      </c>
+      <c r="Q163" s="12" t="n">
+        <v>1657</v>
+      </c>
+      <c r="R163" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="S163" s="12" t="n">
+        <v>937</v>
+      </c>
+      <c r="T163" s="12" t="n">
+        <v>1781</v>
+      </c>
+      <c r="U163" s="12" t="n">
+        <v>2003</v>
+      </c>
+      <c r="V163" s="12" t="n">
+        <v>2152</v>
+      </c>
+      <c r="W163" s="12" t="n">
+        <v>2710</v>
+      </c>
+      <c r="X163" s="12" t="n">
+        <v>5349</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E164" s="12" t="n">
-        <v>-206</v>
-      </c>
-      <c r="I164" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="M164" s="12" t="n">
-        <v>-3621</v>
-      </c>
-      <c r="O164" s="12" t="n">
-        <v>4030</v>
-      </c>
-      <c r="P164" s="12" t="n">
-        <v>-1436</v>
-      </c>
-      <c r="Q164" s="12" t="n">
-        <v>2737</v>
-      </c>
-      <c r="R164" s="12" t="n">
-        <v>-1123</v>
-      </c>
-      <c r="S164" s="12" t="n">
-        <v>859</v>
-      </c>
-      <c r="T164" s="12" t="n">
-        <v>3352</v>
-      </c>
-      <c r="U164" s="12" t="n">
-        <v>-860</v>
-      </c>
-      <c r="V164" s="12" t="n">
-        <v>-206</v>
-      </c>
-      <c r="W164" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="X164" s="12" t="n">
-        <v>-3621</v>
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="E164" s="20" t="n">
+        <v>287</v>
+      </c>
+      <c r="I164" s="20" t="n">
+        <v>478</v>
+      </c>
+      <c r="M164" s="20" t="n">
+        <v>479</v>
+      </c>
+      <c r="O164" s="20" t="n">
+        <v>473</v>
+      </c>
+      <c r="P164" s="20" t="n">
+        <v>655</v>
+      </c>
+      <c r="Q164" s="20" t="n">
+        <v>393</v>
+      </c>
+      <c r="R164" s="20" t="n">
+        <v>259</v>
+      </c>
+      <c r="S164" s="20" t="n">
+        <v>291</v>
+      </c>
+      <c r="T164" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="U164" s="20" t="n">
+        <v>217</v>
+      </c>
+      <c r="V164" s="20" t="n">
+        <v>287</v>
+      </c>
+      <c r="W164" s="20" t="n">
+        <v>478</v>
+      </c>
+      <c r="X164" s="20" t="n">
+        <v>479</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E165" s="20" t="n">
-        <v>-500</v>
+        <v>-89</v>
       </c>
       <c r="I165" s="20" t="n">
-        <v>-415</v>
+        <v>71</v>
       </c>
       <c r="M165" s="20" t="n">
-        <v>-729</v>
+        <v>54</v>
       </c>
       <c r="O165" s="20" t="n">
-        <v>-332</v>
+        <v>0</v>
       </c>
       <c r="P165" s="20" t="n">
-        <v>-368</v>
+        <v>-24</v>
       </c>
       <c r="Q165" s="20" t="n">
-        <v>-245</v>
+        <v>-423</v>
       </c>
       <c r="R165" s="20" t="n">
-        <v>-185</v>
+        <v>157</v>
       </c>
       <c r="S165" s="20" t="n">
-        <v>-221</v>
+        <v>202</v>
       </c>
       <c r="T165" s="20" t="n">
-        <v>-153</v>
+        <v>117</v>
       </c>
       <c r="U165" s="20" t="n">
-        <v>-164</v>
+        <v>9</v>
       </c>
       <c r="V165" s="20" t="n">
-        <v>-500</v>
+        <v>-89</v>
       </c>
       <c r="W165" s="20" t="n">
-        <v>-415</v>
+        <v>71</v>
       </c>
       <c r="X165" s="20" t="n">
-        <v>-729</v>
+        <v>54</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>-20</v>
+        <v>-162</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>-56</v>
+        <v>-165</v>
       </c>
       <c r="M166" s="20" t="n">
-        <v>-134</v>
+        <v>-46</v>
       </c>
       <c r="O166" s="20" t="n">
-        <v>-81</v>
+        <v>25</v>
       </c>
       <c r="P166" s="20" t="n">
-        <v>-61</v>
+        <v>-1414</v>
       </c>
       <c r="Q166" s="20" t="n">
-        <v>-21</v>
+        <v>-181</v>
       </c>
       <c r="R166" s="20" t="n">
-        <v>-40</v>
+        <v>-168</v>
       </c>
       <c r="S166" s="20" t="n">
-        <v>-73</v>
+        <v>-554</v>
       </c>
       <c r="T166" s="20" t="n">
-        <v>-115</v>
+        <v>-127</v>
       </c>
       <c r="U166" s="20" t="n">
-        <v>-38</v>
+        <v>-144</v>
       </c>
       <c r="V166" s="20" t="n">
-        <v>-20</v>
+        <v>-162</v>
       </c>
       <c r="W166" s="20" t="n">
-        <v>-56</v>
+        <v>-165</v>
       </c>
       <c r="X166" s="20" t="n">
-        <v>-134</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>퇴직급여자산 증감</t>
         </is>
       </c>
       <c r="E167" s="20" t="n">
-        <v>0</v>
+        <v>-88</v>
+      </c>
+      <c r="I167" s="20" t="n">
+        <v>-96</v>
+      </c>
+      <c r="M167" s="20" t="n">
+        <v>-94</v>
+      </c>
+      <c r="O167" s="20" t="n">
+        <v>-118</v>
       </c>
       <c r="P167" s="20" t="n">
-        <v>0</v>
+        <v>-78</v>
       </c>
       <c r="Q167" s="20" t="n">
-        <v>131</v>
+        <v>-118</v>
       </c>
       <c r="R167" s="20" t="n">
-        <v>60</v>
+        <v>-224</v>
       </c>
       <c r="S167" s="20" t="n">
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="T167" s="20" t="n">
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="U167" s="20" t="n">
-        <v>350</v>
+        <v>-97</v>
       </c>
       <c r="V167" s="20" t="n">
-        <v>0</v>
+        <v>-88</v>
+      </c>
+      <c r="W167" s="20" t="n">
+        <v>-96</v>
+      </c>
+      <c r="X167" s="20" t="n">
+        <v>-94</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="I168" s="20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M168" s="20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O168" s="20" t="n">
         <v>-0</v>
       </c>
-      <c r="O168" s="20" t="n">
-        <v>3</v>
-      </c>
       <c r="P168" s="20" t="n">
-        <v>12</v>
+        <v>-0</v>
       </c>
       <c r="Q168" s="20" t="n">
-        <v>6</v>
+        <v>-0</v>
       </c>
       <c r="R168" s="20" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
       <c r="S168" s="20" t="n">
-        <v>-6</v>
+        <v>-0</v>
       </c>
       <c r="T168" s="20" t="n">
-        <v>5</v>
+        <v>-0</v>
       </c>
       <c r="U168" s="20" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="V168" s="20" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="W168" s="20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="X168" s="20" t="n">
-        <v>-0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E169" s="12" t="n">
-        <v>-517</v>
-      </c>
-      <c r="I169" s="12" t="n">
-        <v>-471</v>
-      </c>
-      <c r="M169" s="12" t="n">
-        <v>-864</v>
-      </c>
-      <c r="O169" s="12" t="n">
-        <v>-410</v>
-      </c>
-      <c r="P169" s="12" t="n">
-        <v>-418</v>
-      </c>
-      <c r="Q169" s="12" t="n">
-        <v>-129</v>
-      </c>
-      <c r="R169" s="12" t="n">
-        <v>-163</v>
-      </c>
-      <c r="S169" s="12" t="n">
-        <v>-300</v>
-      </c>
-      <c r="T169" s="12" t="n">
-        <v>-263</v>
-      </c>
-      <c r="U169" s="12" t="n">
-        <v>151</v>
-      </c>
-      <c r="V169" s="12" t="n">
-        <v>-517</v>
-      </c>
-      <c r="W169" s="12" t="n">
-        <v>-471</v>
-      </c>
-      <c r="X169" s="12" t="n">
-        <v>-864</v>
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>Gain On Revision Of Retirement Benefit Plan Ope CF</t>
+        </is>
+      </c>
+      <c r="O169" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="20" t="n">
+        <v>-119</v>
+      </c>
+      <c r="Q169" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>1200</v>
+        <v>29</v>
       </c>
       <c r="I170" s="20" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M170" s="20" t="n">
-        <v>4100</v>
+        <v>104</v>
       </c>
       <c r="O170" s="20" t="n">
-        <v>-2464</v>
+        <v>68</v>
       </c>
       <c r="P170" s="20" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="Q170" s="20" t="n">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="R170" s="20" t="n">
-        <v>1300</v>
+        <v>50</v>
       </c>
       <c r="S170" s="20" t="n">
-        <v>320</v>
+        <v>49</v>
       </c>
       <c r="T170" s="20" t="n">
-        <v>-2350</v>
+        <v>38</v>
       </c>
       <c r="U170" s="20" t="n">
-        <v>420</v>
+        <v>26</v>
       </c>
       <c r="V170" s="20" t="n">
-        <v>1200</v>
+        <v>29</v>
       </c>
       <c r="W170" s="20" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="X170" s="20" t="n">
-        <v>4100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>장기차입</t>
-        </is>
-      </c>
-      <c r="E171" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M171" s="20" t="n">
-        <v>2000</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="O171" s="20" t="n">
-        <v>0</v>
+        <v>-3694</v>
       </c>
       <c r="P171" s="20" t="n">
-        <v>4400</v>
+        <v>-1477</v>
       </c>
       <c r="Q171" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T171" s="20" t="n">
-        <v>1900</v>
-      </c>
-      <c r="U171" s="20" t="n">
-        <v>240</v>
-      </c>
-      <c r="V171" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W171" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" s="20" t="n">
-        <v>2000</v>
+        <v>-2400</v>
+      </c>
+      <c r="R171" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="E172" s="20" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I172" s="20" t="n">
-        <v>-60</v>
-      </c>
-      <c r="M172" s="20" t="n">
-        <v>-400</v>
+          <t>Loss On Business Transfer Ope CF</t>
+        </is>
       </c>
       <c r="O172" s="20" t="n">
-        <v>-1641</v>
+        <v>1775</v>
       </c>
       <c r="P172" s="20" t="n">
-        <v>-2308</v>
+        <v>231</v>
       </c>
       <c r="Q172" s="20" t="n">
-        <v>-1805</v>
-      </c>
-      <c r="R172" s="20" t="n">
-        <v>-880</v>
-      </c>
-      <c r="S172" s="20" t="n">
-        <v>-880</v>
-      </c>
-      <c r="T172" s="20" t="n">
-        <v>-880</v>
-      </c>
-      <c r="U172" s="20" t="n">
-        <v>-880</v>
-      </c>
-      <c r="V172" s="20" t="n">
-        <v>-60</v>
-      </c>
-      <c r="W172" s="20" t="n">
-        <v>-60</v>
-      </c>
-      <c r="X172" s="20" t="n">
-        <v>-400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="E173" s="20" t="n">
-        <v>-101</v>
-      </c>
-      <c r="I173" s="20" t="n">
-        <v>-99</v>
-      </c>
-      <c r="M173" s="20" t="n">
-        <v>-91</v>
-      </c>
-      <c r="U173" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V173" s="20" t="n">
-        <v>-101</v>
-      </c>
-      <c r="W173" s="20" t="n">
-        <v>-99</v>
-      </c>
-      <c r="X173" s="20" t="n">
-        <v>-91</v>
+          <t>Decrease In Loss On Business Transfer Ope CF</t>
+        </is>
+      </c>
+      <c r="O173" s="20" t="n">
+        <v>-49</v>
+      </c>
+      <c r="P173" s="20" t="n">
+        <v>-1041</v>
+      </c>
+      <c r="Q173" s="20" t="n">
+        <v>-836</v>
+      </c>
+      <c r="R173" s="20" t="n">
+        <v>-82</v>
+      </c>
+      <c r="S173" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="E174" s="20" t="n">
-        <v>-48</v>
-      </c>
-      <c r="I174" s="20" t="n">
-        <v>-1991</v>
-      </c>
-      <c r="M174" s="20" t="n">
-        <v>-2001</v>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="O174" s="20" t="n">
+        <v>-42</v>
+      </c>
+      <c r="P174" s="20" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q174" s="20" t="n">
+        <v>-579</v>
       </c>
       <c r="R174" s="20" t="n">
-        <v>-0</v>
+        <v>775</v>
       </c>
       <c r="S174" s="20" t="n">
-        <v>-57</v>
+        <v>-311</v>
       </c>
       <c r="T174" s="20" t="n">
-        <v>-1003</v>
-      </c>
-      <c r="U174" s="20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="V174" s="20" t="n">
-        <v>-48</v>
-      </c>
-      <c r="W174" s="20" t="n">
-        <v>-1991</v>
-      </c>
-      <c r="X174" s="20" t="n">
-        <v>-2001</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>Loss Gain On Sales Of Land Ope CF</t>
         </is>
       </c>
       <c r="E175" s="20" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I175" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M175" s="20" t="n">
-        <v>-30</v>
-      </c>
-      <c r="O175" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P175" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q175" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="R175" s="20" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="T175" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="U175" s="20" t="n">
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="V175" s="20" t="n">
-        <v>-33</v>
-      </c>
-      <c r="W175" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="X175" s="20" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E176" s="12" t="n">
-        <v>956</v>
-      </c>
-      <c r="I176" s="12" t="n">
-        <v>-2085</v>
-      </c>
-      <c r="M176" s="12" t="n">
-        <v>3576</v>
-      </c>
-      <c r="O176" s="12" t="n">
-        <v>-4106</v>
-      </c>
-      <c r="P176" s="12" t="n">
-        <v>2190</v>
-      </c>
-      <c r="Q176" s="12" t="n">
-        <v>-1385</v>
-      </c>
-      <c r="R176" s="12" t="n">
-        <v>419</v>
-      </c>
-      <c r="S176" s="12" t="n">
-        <v>-617</v>
-      </c>
-      <c r="T176" s="12" t="n">
-        <v>-2333</v>
-      </c>
-      <c r="U176" s="12" t="n">
-        <v>-230</v>
-      </c>
-      <c r="V176" s="12" t="n">
-        <v>956</v>
-      </c>
-      <c r="W176" s="12" t="n">
-        <v>-2085</v>
-      </c>
-      <c r="X176" s="12" t="n">
-        <v>3576</v>
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>매출채권·계약자산 증감</t>
+        </is>
+      </c>
+      <c r="T176" s="20" t="n">
+        <v>2205</v>
+      </c>
+      <c r="U176" s="20" t="n">
+        <v>-2254</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
+          <t>매출채권·계약자산 증감</t>
+        </is>
+      </c>
+      <c r="E177" s="20" t="n">
+        <v>-1932</v>
+      </c>
+      <c r="I177" s="20" t="n">
+        <v>797</v>
+      </c>
+      <c r="M177" s="20" t="n">
+        <v>-8230</v>
+      </c>
+      <c r="U177" s="20" t="n">
+        <v>-2254</v>
+      </c>
+      <c r="V177" s="20" t="n">
+        <v>-1932</v>
+      </c>
+      <c r="W177" s="20" t="n">
+        <v>797</v>
+      </c>
+      <c r="X177" s="20" t="n">
+        <v>-8230</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="18" t="inlineStr">
+        <is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="E178" s="20" t="n">
+        <v>-426</v>
+      </c>
+      <c r="I178" s="20" t="n">
+        <v>-420</v>
+      </c>
+      <c r="M178" s="20" t="n">
+        <v>-647</v>
+      </c>
+      <c r="O178" s="20" t="n">
+        <v>-89</v>
+      </c>
+      <c r="P178" s="20" t="n">
+        <v>-311</v>
+      </c>
+      <c r="Q178" s="20" t="n">
+        <v>770</v>
+      </c>
+      <c r="R178" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="S178" s="20" t="n">
+        <v>-490</v>
+      </c>
+      <c r="T178" s="20" t="n">
+        <v>665</v>
+      </c>
+      <c r="U178" s="20" t="n">
+        <v>-192</v>
+      </c>
+      <c r="V178" s="20" t="n">
+        <v>-426</v>
+      </c>
+      <c r="W178" s="20" t="n">
+        <v>-420</v>
+      </c>
+      <c r="X178" s="20" t="n">
+        <v>-647</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>매입채무 증감</t>
+        </is>
+      </c>
+      <c r="E179" s="20" t="n">
+        <v>-340</v>
+      </c>
+      <c r="I179" s="20" t="n">
+        <v>-396</v>
+      </c>
+      <c r="M179" s="20" t="n">
+        <v>933</v>
+      </c>
+      <c r="O179" s="20" t="n">
+        <v>392</v>
+      </c>
+      <c r="P179" s="20" t="n">
+        <v>-487</v>
+      </c>
+      <c r="Q179" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="R179" s="20" t="n">
+        <v>-497</v>
+      </c>
+      <c r="S179" s="20" t="n">
+        <v>839</v>
+      </c>
+      <c r="T179" s="20" t="n">
+        <v>-709</v>
+      </c>
+      <c r="U179" s="20" t="n">
+        <v>523</v>
+      </c>
+      <c r="V179" s="20" t="n">
+        <v>-340</v>
+      </c>
+      <c r="W179" s="20" t="n">
+        <v>-396</v>
+      </c>
+      <c r="X179" s="20" t="n">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E180" s="20" t="n">
+        <v>641</v>
+      </c>
+      <c r="I180" s="20" t="n">
+        <v>-457</v>
+      </c>
+      <c r="M180" s="20" t="n">
+        <v>-343</v>
+      </c>
+      <c r="O180" s="20" t="n">
+        <v>-171</v>
+      </c>
+      <c r="P180" s="20" t="n">
+        <v>983</v>
+      </c>
+      <c r="Q180" s="20" t="n">
+        <v>1659</v>
+      </c>
+      <c r="R180" s="20" t="n">
+        <v>-1454</v>
+      </c>
+      <c r="S180" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="T180" s="20" t="n">
+        <v>-717</v>
+      </c>
+      <c r="U180" s="20" t="n">
+        <v>-503</v>
+      </c>
+      <c r="V180" s="20" t="n">
+        <v>641</v>
+      </c>
+      <c r="W180" s="20" t="n">
+        <v>-457</v>
+      </c>
+      <c r="X180" s="20" t="n">
+        <v>-343</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="E181" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="I181" s="20" t="n">
+        <v>2568</v>
+      </c>
+      <c r="M181" s="20" t="n">
+        <v>-2443</v>
+      </c>
+      <c r="O181" s="20" t="n">
+        <v>426</v>
+      </c>
+      <c r="P181" s="20" t="n">
+        <v>-2070</v>
+      </c>
+      <c r="Q181" s="20" t="n">
+        <v>185</v>
+      </c>
+      <c r="R181" s="20" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="S181" s="20" t="n">
+        <v>944</v>
+      </c>
+      <c r="T181" s="20" t="n">
+        <v>3410</v>
+      </c>
+      <c r="U181" s="20" t="n">
+        <v>-497</v>
+      </c>
+      <c r="V181" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="W181" s="20" t="n">
+        <v>2568</v>
+      </c>
+      <c r="X181" s="20" t="n">
+        <v>-2443</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="E182" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M182" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W182" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X182" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="E183" s="20" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I183" s="20" t="n">
+        <v>-45</v>
+      </c>
+      <c r="M183" s="20" t="n">
+        <v>-103</v>
+      </c>
+      <c r="O183" s="20" t="n">
+        <v>-73</v>
+      </c>
+      <c r="P183" s="20" t="n">
+        <v>-56</v>
+      </c>
+      <c r="Q183" s="20" t="n">
+        <v>-67</v>
+      </c>
+      <c r="R183" s="20" t="n">
+        <v>-51</v>
+      </c>
+      <c r="S183" s="20" t="n">
+        <v>-49</v>
+      </c>
+      <c r="T183" s="20" t="n">
+        <v>-40</v>
+      </c>
+      <c r="U183" s="20" t="n">
+        <v>-25</v>
+      </c>
+      <c r="V183" s="20" t="n">
+        <v>-29</v>
+      </c>
+      <c r="W183" s="20" t="n">
+        <v>-45</v>
+      </c>
+      <c r="X183" s="20" t="n">
+        <v>-103</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>보상금 수취</t>
+        </is>
+      </c>
+      <c r="O184" s="20" t="n">
+        <v>3694</v>
+      </c>
+      <c r="P184" s="20" t="n">
+        <v>1477</v>
+      </c>
+      <c r="Q184" s="20" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R184" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
+        <is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="O185" s="20" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P185" s="20" t="n">
+        <v>-788</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr">
+        <is>
+          <t>법인세 납부·환급</t>
+        </is>
+      </c>
+      <c r="E186" s="20" t="n">
+        <v>-247</v>
+      </c>
+      <c r="I186" s="20" t="n">
+        <v>-374</v>
+      </c>
+      <c r="M186" s="20" t="n">
+        <v>-1077</v>
+      </c>
+      <c r="P186" s="20" t="n">
+        <v>-788</v>
+      </c>
+      <c r="Q186" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="R186" s="20" t="n">
+        <v>-21</v>
+      </c>
+      <c r="S186" s="20" t="n">
+        <v>-35</v>
+      </c>
+      <c r="T186" s="20" t="n">
+        <v>-17</v>
+      </c>
+      <c r="U186" s="20" t="n">
+        <v>-338</v>
+      </c>
+      <c r="V186" s="20" t="n">
+        <v>-247</v>
+      </c>
+      <c r="W186" s="20" t="n">
+        <v>-374</v>
+      </c>
+      <c r="X186" s="20" t="n">
+        <v>-1077</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E187" s="12" t="n">
+        <v>-206</v>
+      </c>
+      <c r="I187" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="M187" s="12" t="n">
+        <v>-3621</v>
+      </c>
+      <c r="O187" s="12" t="n">
+        <v>4030</v>
+      </c>
+      <c r="P187" s="12" t="n">
+        <v>-1436</v>
+      </c>
+      <c r="Q187" s="12" t="n">
+        <v>2737</v>
+      </c>
+      <c r="R187" s="12" t="n">
+        <v>-1123</v>
+      </c>
+      <c r="S187" s="12" t="n">
+        <v>859</v>
+      </c>
+      <c r="T187" s="12" t="n">
+        <v>3352</v>
+      </c>
+      <c r="U187" s="12" t="n">
+        <v>-860</v>
+      </c>
+      <c r="V187" s="12" t="n">
+        <v>-206</v>
+      </c>
+      <c r="W187" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="X187" s="12" t="n">
+        <v>-3621</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr">
+        <is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E188" s="20" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I188" s="20" t="n">
+        <v>-415</v>
+      </c>
+      <c r="M188" s="20" t="n">
+        <v>-729</v>
+      </c>
+      <c r="O188" s="20" t="n">
+        <v>-332</v>
+      </c>
+      <c r="P188" s="20" t="n">
+        <v>-368</v>
+      </c>
+      <c r="Q188" s="20" t="n">
+        <v>-245</v>
+      </c>
+      <c r="R188" s="20" t="n">
+        <v>-185</v>
+      </c>
+      <c r="S188" s="20" t="n">
+        <v>-221</v>
+      </c>
+      <c r="T188" s="20" t="n">
+        <v>-153</v>
+      </c>
+      <c r="U188" s="20" t="n">
+        <v>-164</v>
+      </c>
+      <c r="V188" s="20" t="n">
+        <v>-500</v>
+      </c>
+      <c r="W188" s="20" t="n">
+        <v>-415</v>
+      </c>
+      <c r="X188" s="20" t="n">
+        <v>-729</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="18" t="inlineStr">
+        <is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="E189" s="20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I189" s="20" t="n">
+        <v>-56</v>
+      </c>
+      <c r="M189" s="20" t="n">
+        <v>-134</v>
+      </c>
+      <c r="O189" s="20" t="n">
+        <v>-81</v>
+      </c>
+      <c r="P189" s="20" t="n">
+        <v>-61</v>
+      </c>
+      <c r="Q189" s="20" t="n">
+        <v>-21</v>
+      </c>
+      <c r="R189" s="20" t="n">
+        <v>-40</v>
+      </c>
+      <c r="S189" s="20" t="n">
+        <v>-73</v>
+      </c>
+      <c r="T189" s="20" t="n">
+        <v>-115</v>
+      </c>
+      <c r="U189" s="20" t="n">
+        <v>-38</v>
+      </c>
+      <c r="V189" s="20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="W189" s="20" t="n">
+        <v>-56</v>
+      </c>
+      <c r="X189" s="20" t="n">
+        <v>-134</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="inlineStr">
+        <is>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="E190" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="R190" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="S190" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" s="20" t="n">
+        <v>350</v>
+      </c>
+      <c r="V190" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E191" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I191" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O191" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P191" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q191" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R191" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S191" s="20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T191" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U191" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V191" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="W191" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X191" s="20" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="n">
+        <v>-517</v>
+      </c>
+      <c r="I192" s="12" t="n">
+        <v>-471</v>
+      </c>
+      <c r="M192" s="12" t="n">
+        <v>-864</v>
+      </c>
+      <c r="O192" s="12" t="n">
+        <v>-410</v>
+      </c>
+      <c r="P192" s="12" t="n">
+        <v>-418</v>
+      </c>
+      <c r="Q192" s="12" t="n">
+        <v>-129</v>
+      </c>
+      <c r="R192" s="12" t="n">
+        <v>-163</v>
+      </c>
+      <c r="S192" s="12" t="n">
+        <v>-300</v>
+      </c>
+      <c r="T192" s="12" t="n">
+        <v>-263</v>
+      </c>
+      <c r="U192" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="V192" s="12" t="n">
+        <v>-517</v>
+      </c>
+      <c r="W192" s="12" t="n">
+        <v>-471</v>
+      </c>
+      <c r="X192" s="12" t="n">
+        <v>-864</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
+        <is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="E193" s="20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I193" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="M193" s="20" t="n">
+        <v>4100</v>
+      </c>
+      <c r="O193" s="20" t="n">
+        <v>-2464</v>
+      </c>
+      <c r="P193" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q193" s="20" t="n">
+        <v>420</v>
+      </c>
+      <c r="R193" s="20" t="n">
+        <v>1300</v>
+      </c>
+      <c r="S193" s="20" t="n">
+        <v>320</v>
+      </c>
+      <c r="T193" s="20" t="n">
+        <v>-2350</v>
+      </c>
+      <c r="U193" s="20" t="n">
+        <v>420</v>
+      </c>
+      <c r="V193" s="20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="W193" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="X193" s="20" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="E194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" s="20" t="n">
+        <v>4400</v>
+      </c>
+      <c r="Q194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" s="20" t="n">
+        <v>1900</v>
+      </c>
+      <c r="U194" s="20" t="n">
+        <v>240</v>
+      </c>
+      <c r="V194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X194" s="20" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="inlineStr">
+        <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="E195" s="20" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I195" s="20" t="n">
+        <v>-60</v>
+      </c>
+      <c r="M195" s="20" t="n">
+        <v>-400</v>
+      </c>
+      <c r="O195" s="20" t="n">
+        <v>-1641</v>
+      </c>
+      <c r="P195" s="20" t="n">
+        <v>-2308</v>
+      </c>
+      <c r="Q195" s="20" t="n">
+        <v>-1805</v>
+      </c>
+      <c r="R195" s="20" t="n">
+        <v>-880</v>
+      </c>
+      <c r="S195" s="20" t="n">
+        <v>-880</v>
+      </c>
+      <c r="T195" s="20" t="n">
+        <v>-880</v>
+      </c>
+      <c r="U195" s="20" t="n">
+        <v>-880</v>
+      </c>
+      <c r="V195" s="20" t="n">
+        <v>-60</v>
+      </c>
+      <c r="W195" s="20" t="n">
+        <v>-60</v>
+      </c>
+      <c r="X195" s="20" t="n">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E196" s="20" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I196" s="20" t="n">
+        <v>-99</v>
+      </c>
+      <c r="M196" s="20" t="n">
+        <v>-91</v>
+      </c>
+      <c r="U196" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" s="20" t="n">
+        <v>-101</v>
+      </c>
+      <c r="W196" s="20" t="n">
+        <v>-99</v>
+      </c>
+      <c r="X196" s="20" t="n">
+        <v>-91</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E197" s="20" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I197" s="20" t="n">
+        <v>-1991</v>
+      </c>
+      <c r="M197" s="20" t="n">
+        <v>-2001</v>
+      </c>
+      <c r="R197" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S197" s="20" t="n">
+        <v>-57</v>
+      </c>
+      <c r="T197" s="20" t="n">
+        <v>-1003</v>
+      </c>
+      <c r="U197" s="20" t="n">
+        <v>-10</v>
+      </c>
+      <c r="V197" s="20" t="n">
+        <v>-48</v>
+      </c>
+      <c r="W197" s="20" t="n">
+        <v>-1991</v>
+      </c>
+      <c r="X197" s="20" t="n">
+        <v>-2001</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E198" s="20" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I198" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M198" s="20" t="n">
+        <v>-30</v>
+      </c>
+      <c r="O198" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P198" s="20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q198" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R198" s="20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U198" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" s="20" t="n">
+        <v>-33</v>
+      </c>
+      <c r="W198" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="X198" s="20" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E199" s="12" t="n">
+        <v>956</v>
+      </c>
+      <c r="I199" s="12" t="n">
+        <v>-2085</v>
+      </c>
+      <c r="M199" s="12" t="n">
+        <v>3576</v>
+      </c>
+      <c r="O199" s="12" t="n">
+        <v>-4106</v>
+      </c>
+      <c r="P199" s="12" t="n">
+        <v>2190</v>
+      </c>
+      <c r="Q199" s="12" t="n">
+        <v>-1385</v>
+      </c>
+      <c r="R199" s="12" t="n">
+        <v>419</v>
+      </c>
+      <c r="S199" s="12" t="n">
+        <v>-617</v>
+      </c>
+      <c r="T199" s="12" t="n">
+        <v>-2333</v>
+      </c>
+      <c r="U199" s="12" t="n">
+        <v>-230</v>
+      </c>
+      <c r="V199" s="12" t="n">
+        <v>956</v>
+      </c>
+      <c r="W199" s="12" t="n">
+        <v>-2085</v>
+      </c>
+      <c r="X199" s="12" t="n">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E177" s="20" t="n">
+      <c r="E200" s="20" t="n">
         <v>233</v>
       </c>
-      <c r="I177" s="20" t="n">
+      <c r="I200" s="20" t="n">
         <v>-407</v>
       </c>
-      <c r="M177" s="20" t="n">
+      <c r="M200" s="20" t="n">
         <v>-909</v>
       </c>
-      <c r="O177" s="20" t="n">
+      <c r="O200" s="20" t="n">
         <v>-486</v>
       </c>
-      <c r="P177" s="20" t="n">
+      <c r="P200" s="20" t="n">
         <v>335</v>
       </c>
-      <c r="Q177" s="20" t="n">
+      <c r="Q200" s="20" t="n">
         <v>1222</v>
       </c>
-      <c r="R177" s="20" t="n">
+      <c r="R200" s="20" t="n">
         <v>-866</v>
       </c>
-      <c r="S177" s="20" t="n">
+      <c r="S200" s="20" t="n">
         <v>-58</v>
       </c>
-      <c r="T177" s="20" t="n">
+      <c r="T200" s="20" t="n">
         <v>756</v>
       </c>
-      <c r="U177" s="20" t="n">
+      <c r="U200" s="20" t="n">
         <v>-938</v>
       </c>
-      <c r="V177" s="20" t="n">
+      <c r="V200" s="20" t="n">
         <v>233</v>
       </c>
-      <c r="W177" s="20" t="n">
+      <c r="W200" s="20" t="n">
         <v>-407</v>
       </c>
-      <c r="X177" s="20" t="n">
+      <c r="X200" s="20" t="n">
         <v>-909</v>
       </c>
     </row>
@@ -10497,7 +11840,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11917,7 +13260,7 @@
       <c r="L42" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="44" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11969,7 +13312,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -12021,7 +13364,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -12073,7 +13416,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="inlineStr">
+      <c r="A46" s="45" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -12125,7 +13468,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12177,7 +13520,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12229,7 +13572,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12239,43 +13582,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="45">
+      <c r="C49" s="46">
         <f>IFERROR(IF((IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="46">
+      <c r="D49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="46">
+      <c r="E49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="46">
+      <c r="F49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="46">
+      <c r="G49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!K47:N47)&lt;4,"",SUM('연간'!K47:N47)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K47:N47)&lt;4,"",SUM('연간'!K47:N47)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="46">
         <f>IFERROR(IF(('연간'!T47)&lt;=0,"적자",H28/('연간'!T47)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="47">
         <f>IFERROR(IF(('연간'!U47)&lt;=0,"적자",I28/('연간'!U47)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="47">
         <f>IFERROR(IF(('연간'!V47)&lt;=0,"적자",J28/('연간'!V47)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="47">
         <f>IFERROR(IF(('연간'!W47)&lt;=0,"적자",K28/('연간'!W47)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="47">
         <f>IFERROR(IF(('연간'!X47)&lt;=0,"적자",L28/('연간'!X47)),"")</f>
         <v/>
       </c>
@@ -12299,7 +13642,7 @@
       <c r="L50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12351,7 +13694,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12403,7 +13746,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12455,7 +13798,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="44" t="inlineStr">
+      <c r="A54" s="45" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12507,7 +13850,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="45" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12559,7 +13902,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12629,7 +13972,7 @@
       <c r="L57" s="23" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12681,7 +14024,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="44" t="inlineStr">
+      <c r="A59" s="45" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12691,49 +14034,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="48">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="48">
+      <c r="D59" s="49">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="49">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="48">
+      <c r="F59" s="49">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="48">
+      <c r="G59" s="49">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="48">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="48">
+      <c r="I59" s="49">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="48">
+      <c r="J59" s="49">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="48">
+      <c r="K59" s="49">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="48">
+      <c r="L59" s="49">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="inlineStr">
+      <c r="A60" s="45" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12743,49 +14086,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <f>IFERROR(C9/(IF(COUNT('연간'!G14:J14)&lt;4,"",SUM('연간'!G14:J14)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="48">
+      <c r="D60" s="49">
         <f>IFERROR(D9/(IF(COUNT('연간'!H14:K14)&lt;4,"",SUM('연간'!H14:K14)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="49">
         <f>IFERROR(E9/(IF(COUNT('연간'!I14:L14)&lt;4,"",SUM('연간'!I14:L14)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="48">
+      <c r="F60" s="49">
         <f>IFERROR(F9/(IF(COUNT('연간'!J14:M14)&lt;4,"",SUM('연간'!J14:M14)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="48">
+      <c r="G60" s="49">
         <f>IFERROR(G9/(IF(COUNT('연간'!K14:N14)&lt;4,"",SUM('연간'!K14:N14)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="47">
+      <c r="H60" s="48">
         <f>IFERROR(H9/('연간'!T14)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="48">
+      <c r="I60" s="49">
         <f>IFERROR(I9/('연간'!U14)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="48">
+      <c r="J60" s="49">
         <f>IFERROR(J9/('연간'!V14)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="48">
+      <c r="K60" s="49">
         <f>IFERROR(K9/('연간'!W14)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="48">
+      <c r="L60" s="49">
         <f>IFERROR(L9/('연간'!X14)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="A61" s="45" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12795,49 +14138,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="48">
         <f>IFERROR(C19/(IF(COUNT('연간'!G14:J14)&lt;4,"",SUM('연간'!G14:J14)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="48">
+      <c r="D61" s="49">
         <f>IFERROR(D19/(IF(COUNT('연간'!H14:K14)&lt;4,"",SUM('연간'!H14:K14)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="49">
         <f>IFERROR(E19/(IF(COUNT('연간'!I14:L14)&lt;4,"",SUM('연간'!I14:L14)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="48">
+      <c r="F61" s="49">
         <f>IFERROR(F19/(IF(COUNT('연간'!J14:M14)&lt;4,"",SUM('연간'!J14:M14)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="48">
+      <c r="G61" s="49">
         <f>IFERROR(G19/(IF(COUNT('연간'!K14:N14)&lt;4,"",SUM('연간'!K14:N14)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="47">
+      <c r="H61" s="48">
         <f>IFERROR(H19/('연간'!T14)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="48">
+      <c r="I61" s="49">
         <f>IFERROR(I19/('연간'!U14)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="48">
+      <c r="J61" s="49">
         <f>IFERROR(J19/('연간'!V14)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="48">
+      <c r="K61" s="49">
         <f>IFERROR(K19/('연간'!W14)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="48">
+      <c r="L61" s="49">
         <f>IFERROR(L19/('연간'!X14)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="44" t="inlineStr">
+      <c r="A62" s="45" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12847,43 +14190,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="48">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="48">
+      <c r="D62" s="49">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="49">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="49">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="48">
+      <c r="G62" s="49">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="47">
+      <c r="H62" s="48">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="48">
+      <c r="I62" s="49">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="48">
+      <c r="J62" s="49">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="48">
+      <c r="K62" s="49">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="49">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12907,7 +14250,7 @@
       <c r="L63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="A64" s="45" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12959,7 +14302,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="A65" s="45" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -13011,7 +14354,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="A66" s="45" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -13063,7 +14406,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="A67" s="45" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15466,24 +16809,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
